--- a/research/traditional_assets/database/data/peru/peru_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_retail_distributors.xlsx
@@ -1151,7 +1151,7 @@
         <v>730</v>
       </c>
       <c r="L2">
-        <v>578.457373636198</v>
+        <v>578.457373636197</v>
       </c>
       <c r="M2">
         <v>1265</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.083202787159014</v>
+        <v>0.08298906393689491</v>
       </c>
       <c r="C2">
-        <v>1225.838837641478</v>
+        <v>1216.621556525412</v>
       </c>
       <c r="D2">
-        <v>1189.238837641478</v>
+        <v>1193.037556525413</v>
       </c>
       <c r="E2">
-        <v>-571.6</v>
+        <v>-558.5840000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13.016</v>
       </c>
       <c r="G2">
         <v>36.6</v>
@@ -1451,28 +1451,28 @@
         <v>230.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6547048</v>
       </c>
       <c r="N2">
-        <v>230.3</v>
+        <v>229.6452952</v>
       </c>
       <c r="O2">
-        <v>67.9385</v>
+        <v>67.74536208400001</v>
       </c>
       <c r="P2">
-        <v>162.3615</v>
+        <v>161.899933116</v>
       </c>
       <c r="Q2">
-        <v>198.4615</v>
+        <v>197.999933116</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.083202787159014</v>
+        <v>0.08346914034029788</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5827296208421914</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>351.7615878178991</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08298906393689491</v>
+        <v>0.08277534071477582</v>
       </c>
       <c r="C3">
-        <v>1216.621556525412</v>
+        <v>1207.428621245009</v>
       </c>
       <c r="D3">
-        <v>1193.037556525413</v>
+        <v>1196.860621245009</v>
       </c>
       <c r="E3">
-        <v>-558.5840000000001</v>
+        <v>-545.568</v>
       </c>
       <c r="F3">
-        <v>13.016</v>
+        <v>26.032</v>
       </c>
       <c r="G3">
         <v>36.6</v>
@@ -1533,28 +1533,28 @@
         <v>230.3</v>
       </c>
       <c r="M3">
-        <v>0.6547048</v>
+        <v>1.3094096</v>
       </c>
       <c r="N3">
-        <v>229.6452952</v>
+        <v>228.9905904</v>
       </c>
       <c r="O3">
-        <v>67.74536208400001</v>
+        <v>67.552224168</v>
       </c>
       <c r="P3">
-        <v>161.899933116</v>
+        <v>161.438366232</v>
       </c>
       <c r="Q3">
-        <v>197.999933116</v>
+        <v>197.538366232</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08346914034029788</v>
+        <v>0.08374092930079165</v>
       </c>
       <c r="T3">
-        <v>0.5827296208421914</v>
+        <v>0.5869341096217825</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>351.7615878178991</v>
+        <v>175.8807939089495</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08277534071477582</v>
+        <v>0.08256161749265671</v>
       </c>
       <c r="C4">
-        <v>1207.428621245009</v>
+        <v>1198.260266599893</v>
       </c>
       <c r="D4">
-        <v>1196.860621245009</v>
+        <v>1200.708266599893</v>
       </c>
       <c r="E4">
-        <v>-545.568</v>
+        <v>-532.552</v>
       </c>
       <c r="F4">
-        <v>26.032</v>
+        <v>39.04799999999999</v>
       </c>
       <c r="G4">
         <v>36.6</v>
@@ -1615,28 +1615,28 @@
         <v>230.3</v>
       </c>
       <c r="M4">
-        <v>1.3094096</v>
+        <v>1.9641144</v>
       </c>
       <c r="N4">
-        <v>228.9905904</v>
+        <v>228.3358856</v>
       </c>
       <c r="O4">
-        <v>67.552224168</v>
+        <v>67.359086252</v>
       </c>
       <c r="P4">
-        <v>161.438366232</v>
+        <v>160.976799348</v>
       </c>
       <c r="Q4">
-        <v>197.538366232</v>
+        <v>197.076799348</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08374092930079165</v>
+        <v>0.08401832215737806</v>
       </c>
       <c r="T4">
-        <v>0.5869341096217825</v>
+        <v>0.5912252888916745</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>175.8807939089495</v>
+        <v>117.2538626059664</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08256161749265671</v>
+        <v>0.08234789427053762</v>
       </c>
       <c r="C5">
-        <v>1198.260266599893</v>
+        <v>1189.116730418743</v>
       </c>
       <c r="D5">
-        <v>1200.708266599893</v>
+        <v>1204.580730418743</v>
       </c>
       <c r="E5">
-        <v>-532.552</v>
+        <v>-519.5360000000001</v>
       </c>
       <c r="F5">
-        <v>39.04799999999999</v>
+        <v>52.064</v>
       </c>
       <c r="G5">
         <v>36.6</v>
@@ -1697,28 +1697,28 @@
         <v>230.3</v>
       </c>
       <c r="M5">
-        <v>1.9641144</v>
+        <v>2.6188192</v>
       </c>
       <c r="N5">
-        <v>228.3358856</v>
+        <v>227.6811808</v>
       </c>
       <c r="O5">
-        <v>67.359086252</v>
+        <v>67.165948336</v>
       </c>
       <c r="P5">
-        <v>160.976799348</v>
+        <v>160.515232464</v>
       </c>
       <c r="Q5">
-        <v>197.076799348</v>
+        <v>196.615232464</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08401832215737806</v>
+        <v>0.08430149403181003</v>
       </c>
       <c r="T5">
-        <v>0.5912252888916745</v>
+        <v>0.595605867729689</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>117.2538626059664</v>
+        <v>87.94039695447476</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08234789427053762</v>
+        <v>0.08213417104841854</v>
       </c>
       <c r="C6">
-        <v>1189.116730418743</v>
+        <v>1179.998253608299</v>
       </c>
       <c r="D6">
-        <v>1204.580730418743</v>
+        <v>1208.478253608299</v>
       </c>
       <c r="E6">
-        <v>-519.5360000000001</v>
+        <v>-506.52</v>
       </c>
       <c r="F6">
-        <v>52.064</v>
+        <v>65.08</v>
       </c>
       <c r="G6">
         <v>36.6</v>
@@ -1779,28 +1779,28 @@
         <v>230.3</v>
       </c>
       <c r="M6">
-        <v>2.6188192</v>
+        <v>3.273524</v>
       </c>
       <c r="N6">
-        <v>227.6811808</v>
+        <v>227.026476</v>
       </c>
       <c r="O6">
-        <v>67.165948336</v>
+        <v>66.97281042</v>
       </c>
       <c r="P6">
-        <v>160.515232464</v>
+        <v>160.05366558</v>
       </c>
       <c r="Q6">
-        <v>196.615232464</v>
+        <v>196.15366558</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08430149403181003</v>
+        <v>0.08459062741938794</v>
       </c>
       <c r="T6">
-        <v>0.595605867729689</v>
+        <v>0.600078669280083</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>87.94039695447476</v>
+        <v>70.3523175635798</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08213417104841854</v>
+        <v>0.08192044782629944</v>
       </c>
       <c r="C7">
-        <v>1179.998253608299</v>
+        <v>1170.90508020332</v>
       </c>
       <c r="D7">
-        <v>1208.478253608299</v>
+        <v>1212.40108020332</v>
       </c>
       <c r="E7">
-        <v>-506.52</v>
+        <v>-493.504</v>
       </c>
       <c r="F7">
-        <v>65.08</v>
+        <v>78.096</v>
       </c>
       <c r="G7">
         <v>36.6</v>
@@ -1861,28 +1861,28 @@
         <v>230.3</v>
       </c>
       <c r="M7">
-        <v>3.273524</v>
+        <v>3.9282288</v>
       </c>
       <c r="N7">
-        <v>227.026476</v>
+        <v>226.3717712</v>
       </c>
       <c r="O7">
-        <v>66.97281042</v>
+        <v>66.779672504</v>
       </c>
       <c r="P7">
-        <v>160.05366558</v>
+        <v>159.592098696</v>
       </c>
       <c r="Q7">
-        <v>196.15366558</v>
+        <v>195.692098696</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08459062741938794</v>
+        <v>0.08488591258116962</v>
       </c>
       <c r="T7">
-        <v>0.600078669280083</v>
+        <v>0.6046466368209108</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>70.3523175635798</v>
+        <v>58.62693130298317</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08192044782629944</v>
+        <v>0.08170672460418037</v>
       </c>
       <c r="C8">
-        <v>1170.90508020332</v>
+        <v>1161.837457417513</v>
       </c>
       <c r="D8">
-        <v>1212.40108020332</v>
+        <v>1216.349457417513</v>
       </c>
       <c r="E8">
-        <v>-493.504</v>
+        <v>-480.4880000000001</v>
       </c>
       <c r="F8">
-        <v>78.09599999999999</v>
+        <v>91.11199999999998</v>
       </c>
       <c r="G8">
         <v>36.6</v>
@@ -1943,28 +1943,28 @@
         <v>230.3</v>
       </c>
       <c r="M8">
-        <v>3.928228799999999</v>
+        <v>4.582933599999999</v>
       </c>
       <c r="N8">
-        <v>226.3717712</v>
+        <v>225.7170664</v>
       </c>
       <c r="O8">
-        <v>66.779672504</v>
+        <v>66.58653458800001</v>
       </c>
       <c r="P8">
-        <v>159.592098696</v>
+        <v>159.130531812</v>
       </c>
       <c r="Q8">
-        <v>195.692098696</v>
+        <v>195.230531812</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08488591258116962</v>
+        <v>0.08518754796148426</v>
       </c>
       <c r="T8">
-        <v>0.6046466368209108</v>
+        <v>0.6093128402228317</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>58.62693130298318</v>
+        <v>50.25165540255702</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08170672460418035</v>
+        <v>0.08149300138206128</v>
       </c>
       <c r="C9">
-        <v>1161.837457417513</v>
+        <v>1152.795635695476</v>
       </c>
       <c r="D9">
-        <v>1216.349457417513</v>
+        <v>1220.323635695476</v>
       </c>
       <c r="E9">
-        <v>-480.488</v>
+        <v>-467.472</v>
       </c>
       <c r="F9">
-        <v>91.11200000000001</v>
+        <v>104.128</v>
       </c>
       <c r="G9">
         <v>36.6</v>
@@ -2025,28 +2025,28 @@
         <v>230.3</v>
       </c>
       <c r="M9">
-        <v>4.5829336</v>
+        <v>5.2376384</v>
       </c>
       <c r="N9">
-        <v>225.7170664</v>
+        <v>225.0623616</v>
       </c>
       <c r="O9">
-        <v>66.58653458800001</v>
+        <v>66.39339667199999</v>
       </c>
       <c r="P9">
-        <v>159.130531812</v>
+        <v>158.668964928</v>
       </c>
       <c r="Q9">
-        <v>195.230531812</v>
+        <v>194.768964928</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08518754796148426</v>
+        <v>0.08549574063267529</v>
       </c>
       <c r="T9">
-        <v>0.6093128402228317</v>
+        <v>0.6140804828291422</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>50.251655402557</v>
+        <v>43.97019847723737</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08149300138206128</v>
+        <v>0.08127927815994218</v>
       </c>
       <c r="C10">
-        <v>1152.795635695476</v>
+        <v>1143.779868765641</v>
       </c>
       <c r="D10">
-        <v>1220.323635695476</v>
+        <v>1224.323868765641</v>
       </c>
       <c r="E10">
-        <v>-467.472</v>
+        <v>-454.456</v>
       </c>
       <c r="F10">
-        <v>104.128</v>
+        <v>117.144</v>
       </c>
       <c r="G10">
         <v>36.6</v>
@@ -2107,28 +2107,28 @@
         <v>230.3</v>
       </c>
       <c r="M10">
-        <v>5.2376384</v>
+        <v>5.892343199999999</v>
       </c>
       <c r="N10">
-        <v>225.0623616</v>
+        <v>224.4076568</v>
       </c>
       <c r="O10">
-        <v>66.39339667199999</v>
+        <v>66.200258756</v>
       </c>
       <c r="P10">
-        <v>158.668964928</v>
+        <v>158.207398044</v>
       </c>
       <c r="Q10">
-        <v>194.768964928</v>
+        <v>194.307398044</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08549574063267529</v>
+        <v>0.08581070676916723</v>
       </c>
       <c r="T10">
-        <v>0.6140804828291422</v>
+        <v>0.6189529087894377</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>43.97019847723737</v>
+        <v>39.08462086865545</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08127927815994218</v>
+        <v>0.08106555493782308</v>
       </c>
       <c r="C11">
-        <v>1143.779868765641</v>
+        <v>1134.790413694283</v>
       </c>
       <c r="D11">
-        <v>1224.323868765641</v>
+        <v>1228.350413694283</v>
       </c>
       <c r="E11">
-        <v>-454.456</v>
+        <v>-441.4400000000001</v>
       </c>
       <c r="F11">
-        <v>117.144</v>
+        <v>130.16</v>
       </c>
       <c r="G11">
         <v>36.6</v>
@@ -2189,28 +2189,28 @@
         <v>230.3</v>
       </c>
       <c r="M11">
-        <v>5.892343199999999</v>
+        <v>6.547047999999998</v>
       </c>
       <c r="N11">
-        <v>224.4076568</v>
+        <v>223.752952</v>
       </c>
       <c r="O11">
-        <v>66.200258756</v>
+        <v>66.00712084</v>
       </c>
       <c r="P11">
-        <v>158.207398044</v>
+        <v>157.74583116</v>
       </c>
       <c r="Q11">
-        <v>194.307398044</v>
+        <v>193.84583116</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08581070676916723</v>
+        <v>0.08613267215313676</v>
       </c>
       <c r="T11">
-        <v>0.6189529087894377</v>
+        <v>0.6239336108821839</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>39.08462086865545</v>
+        <v>35.17615878178991</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08106555493782308</v>
+        <v>0.080851831715704</v>
       </c>
       <c r="C12">
-        <v>1134.790413694283</v>
+        <v>1125.827530940582</v>
       </c>
       <c r="D12">
-        <v>1228.350413694283</v>
+        <v>1232.403530940582</v>
       </c>
       <c r="E12">
-        <v>-441.4400000000001</v>
+        <v>-428.424</v>
       </c>
       <c r="F12">
-        <v>130.16</v>
+        <v>143.176</v>
       </c>
       <c r="G12">
         <v>36.6</v>
@@ -2271,28 +2271,28 @@
         <v>230.3</v>
       </c>
       <c r="M12">
-        <v>6.547047999999999</v>
+        <v>7.201752799999999</v>
       </c>
       <c r="N12">
-        <v>223.752952</v>
+        <v>223.0982472</v>
       </c>
       <c r="O12">
-        <v>66.00712084</v>
+        <v>65.813982924</v>
       </c>
       <c r="P12">
-        <v>157.74583116</v>
+        <v>157.284264276</v>
       </c>
       <c r="Q12">
-        <v>193.84583116</v>
+        <v>193.384264276</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08613267215313676</v>
+        <v>0.08646187271427415</v>
       </c>
       <c r="T12">
-        <v>0.6239336108821839</v>
+        <v>0.6290262388646549</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>35.17615878178991</v>
+        <v>31.97832616526355</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.080851831715704</v>
+        <v>0.08063810849358491</v>
       </c>
       <c r="C13">
-        <v>1125.827530940582</v>
+        <v>1116.891484412787</v>
       </c>
       <c r="D13">
-        <v>1232.403530940582</v>
+        <v>1236.483484412787</v>
       </c>
       <c r="E13">
-        <v>-428.424</v>
+        <v>-415.408</v>
       </c>
       <c r="F13">
-        <v>143.176</v>
+        <v>156.192</v>
       </c>
       <c r="G13">
         <v>36.6</v>
@@ -2353,28 +2353,28 @@
         <v>230.3</v>
       </c>
       <c r="M13">
-        <v>7.201752799999999</v>
+        <v>7.856457599999999</v>
       </c>
       <c r="N13">
-        <v>223.0982472</v>
+        <v>222.4435424</v>
       </c>
       <c r="O13">
-        <v>65.813982924</v>
+        <v>65.620845008</v>
       </c>
       <c r="P13">
-        <v>157.284264276</v>
+        <v>156.822697392</v>
       </c>
       <c r="Q13">
-        <v>193.384264276</v>
+        <v>192.922697392</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08646187271427415</v>
+        <v>0.08679855510634649</v>
       </c>
       <c r="T13">
-        <v>0.6290262388646549</v>
+        <v>0.634234608392182</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>31.97832616526355</v>
+        <v>29.31346565149159</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08063810849358491</v>
+        <v>0.08042438527146581</v>
       </c>
       <c r="C14">
-        <v>1116.891484412787</v>
+        <v>1107.9825415255</v>
       </c>
       <c r="D14">
-        <v>1236.483484412787</v>
+        <v>1240.590541525501</v>
       </c>
       <c r="E14">
-        <v>-415.408</v>
+        <v>-402.3920000000001</v>
       </c>
       <c r="F14">
-        <v>156.192</v>
+        <v>169.208</v>
       </c>
       <c r="G14">
         <v>36.6</v>
@@ -2435,28 +2435,28 @@
         <v>230.3</v>
       </c>
       <c r="M14">
-        <v>7.856457599999999</v>
+        <v>8.5111624</v>
       </c>
       <c r="N14">
-        <v>222.4435424</v>
+        <v>221.7888376</v>
       </c>
       <c r="O14">
-        <v>65.620845008</v>
+        <v>65.42770709200001</v>
       </c>
       <c r="P14">
-        <v>156.822697392</v>
+        <v>156.361130508</v>
       </c>
       <c r="Q14">
-        <v>192.922697392</v>
+        <v>192.461130508</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08679855510634649</v>
+        <v>0.08714297732352391</v>
       </c>
       <c r="T14">
-        <v>0.634234608392182</v>
+        <v>0.6395627105525259</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.31346565149159</v>
+        <v>27.05858367829993</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08042438527146581</v>
+        <v>0.08021066204934671</v>
       </c>
       <c r="C15">
-        <v>1107.9825415255</v>
+        <v>1099.1009732581</v>
       </c>
       <c r="D15">
-        <v>1240.590541525501</v>
+        <v>1244.7249732581</v>
       </c>
       <c r="E15">
-        <v>-402.3920000000001</v>
+        <v>-389.376</v>
       </c>
       <c r="F15">
-        <v>169.208</v>
+        <v>182.224</v>
       </c>
       <c r="G15">
         <v>36.6</v>
@@ -2517,28 +2517,28 @@
         <v>230.3</v>
       </c>
       <c r="M15">
-        <v>8.5111624</v>
+        <v>9.165867200000001</v>
       </c>
       <c r="N15">
-        <v>221.7888376</v>
+        <v>221.1341328</v>
       </c>
       <c r="O15">
-        <v>65.42770709200001</v>
+        <v>65.23456917599999</v>
       </c>
       <c r="P15">
-        <v>156.361130508</v>
+        <v>155.899563624</v>
       </c>
       <c r="Q15">
-        <v>192.461130508</v>
+        <v>191.999563624</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08714297732352391</v>
+        <v>0.08749540935970548</v>
       </c>
       <c r="T15">
-        <v>0.6395627105525259</v>
+        <v>0.6450147220654359</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.05858367829993</v>
+        <v>25.1258277012785</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08021066204934671</v>
+        <v>0.07999693882722762</v>
       </c>
       <c r="C16">
-        <v>1099.1009732581</v>
+        <v>1090.247054214341</v>
       </c>
       <c r="D16">
-        <v>1244.7249732581</v>
+        <v>1248.887054214341</v>
       </c>
       <c r="E16">
-        <v>-389.376</v>
+        <v>-376.36</v>
       </c>
       <c r="F16">
-        <v>182.224</v>
+        <v>195.24</v>
       </c>
       <c r="G16">
         <v>36.6</v>
@@ -2599,28 +2599,28 @@
         <v>230.3</v>
       </c>
       <c r="M16">
-        <v>9.165867200000001</v>
+        <v>9.820572</v>
       </c>
       <c r="N16">
-        <v>221.1341328</v>
+        <v>220.479428</v>
       </c>
       <c r="O16">
-        <v>65.23456917599999</v>
+        <v>65.04143126</v>
       </c>
       <c r="P16">
-        <v>155.899563624</v>
+        <v>155.43799674</v>
       </c>
       <c r="Q16">
-        <v>191.999563624</v>
+        <v>191.53799674</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08749540935970548</v>
+        <v>0.08785613391438545</v>
       </c>
       <c r="T16">
-        <v>0.6450147220654359</v>
+        <v>0.6505950162021791</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.1258277012785</v>
+        <v>23.45077252119327</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07999693882722762</v>
+        <v>0.07978321560510854</v>
       </c>
       <c r="C17">
-        <v>1090.247054214341</v>
+        <v>1081.421062683155</v>
       </c>
       <c r="D17">
-        <v>1248.887054214341</v>
+        <v>1253.077062683155</v>
       </c>
       <c r="E17">
-        <v>-376.36</v>
+        <v>-363.3440000000001</v>
       </c>
       <c r="F17">
-        <v>195.24</v>
+        <v>208.256</v>
       </c>
       <c r="G17">
         <v>36.6</v>
@@ -2681,28 +2681,28 @@
         <v>230.3</v>
       </c>
       <c r="M17">
-        <v>9.820571999999999</v>
+        <v>10.4752768</v>
       </c>
       <c r="N17">
-        <v>220.479428</v>
+        <v>219.8247232</v>
       </c>
       <c r="O17">
-        <v>65.04143126</v>
+        <v>64.848293344</v>
       </c>
       <c r="P17">
-        <v>155.43799674</v>
+        <v>154.976429856</v>
       </c>
       <c r="Q17">
-        <v>191.53799674</v>
+        <v>191.076429856</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08785613391438545</v>
+        <v>0.08822544714893873</v>
       </c>
       <c r="T17">
-        <v>0.6505950162021791</v>
+        <v>0.6563081744850352</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.45077252119327</v>
+        <v>21.98509923861869</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07978321560510854</v>
+        <v>0.07956949238298945</v>
       </c>
       <c r="C18">
-        <v>1081.421062683155</v>
+        <v>1072.623280700677</v>
       </c>
       <c r="D18">
-        <v>1253.077062683155</v>
+        <v>1257.295280700677</v>
       </c>
       <c r="E18">
-        <v>-363.3440000000001</v>
+        <v>-350.328</v>
       </c>
       <c r="F18">
-        <v>208.256</v>
+        <v>221.272</v>
       </c>
       <c r="G18">
         <v>36.6</v>
@@ -2763,28 +2763,28 @@
         <v>230.3</v>
       </c>
       <c r="M18">
-        <v>10.4752768</v>
+        <v>11.1299816</v>
       </c>
       <c r="N18">
-        <v>219.8247232</v>
+        <v>219.1700184</v>
       </c>
       <c r="O18">
-        <v>64.848293344</v>
+        <v>64.655155428</v>
       </c>
       <c r="P18">
-        <v>154.976429856</v>
+        <v>154.514862972</v>
       </c>
       <c r="Q18">
-        <v>191.076429856</v>
+        <v>190.614862972</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08822544714893873</v>
+        <v>0.08860365949757765</v>
       </c>
       <c r="T18">
-        <v>0.6563081744850352</v>
+        <v>0.6621589992325384</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.98509923861869</v>
+        <v>20.69185810693524</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07956949238298945</v>
+        <v>0.07935576916087037</v>
       </c>
       <c r="C19">
-        <v>1072.623280700677</v>
+        <v>1063.853994113525</v>
       </c>
       <c r="D19">
-        <v>1257.295280700677</v>
+        <v>1261.541994113526</v>
       </c>
       <c r="E19">
-        <v>-350.328</v>
+        <v>-337.312</v>
       </c>
       <c r="F19">
-        <v>221.272</v>
+        <v>234.288</v>
       </c>
       <c r="G19">
         <v>36.6</v>
@@ -2845,28 +2845,28 @@
         <v>230.3</v>
       </c>
       <c r="M19">
-        <v>11.1299816</v>
+        <v>11.7846864</v>
       </c>
       <c r="N19">
-        <v>219.1700184</v>
+        <v>218.5153136</v>
       </c>
       <c r="O19">
-        <v>64.655155428</v>
+        <v>64.462017512</v>
       </c>
       <c r="P19">
-        <v>154.514862972</v>
+        <v>154.053296088</v>
       </c>
       <c r="Q19">
-        <v>190.614862972</v>
+        <v>190.153296088</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08860365949757765</v>
+        <v>0.08899109653764678</v>
       </c>
       <c r="T19">
-        <v>0.6621589992325384</v>
+        <v>0.6681525270226637</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.69185810693524</v>
+        <v>19.54231043432772</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07935576916087037</v>
+        <v>0.07914204593875127</v>
       </c>
       <c r="C20">
-        <v>1063.853994113525</v>
+        <v>1055.113492643379</v>
       </c>
       <c r="D20">
-        <v>1261.541994113526</v>
+        <v>1265.817492643379</v>
       </c>
       <c r="E20">
-        <v>-337.312</v>
+        <v>-324.296</v>
       </c>
       <c r="F20">
-        <v>234.288</v>
+        <v>247.304</v>
       </c>
       <c r="G20">
         <v>36.6</v>
@@ -2927,28 +2927,28 @@
         <v>230.3</v>
       </c>
       <c r="M20">
-        <v>11.7846864</v>
+        <v>12.4393912</v>
       </c>
       <c r="N20">
-        <v>218.5153136</v>
+        <v>217.8606088</v>
       </c>
       <c r="O20">
-        <v>64.462017512</v>
+        <v>64.268879596</v>
       </c>
       <c r="P20">
-        <v>154.053296088</v>
+        <v>153.591729204</v>
       </c>
       <c r="Q20">
-        <v>190.153296088</v>
+        <v>189.691729204</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08899109653764678</v>
+        <v>0.08938809992438428</v>
       </c>
       <c r="T20">
-        <v>0.6681525270226637</v>
+        <v>0.6742940431532858</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.54231043432772</v>
+        <v>18.51376777988943</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07914204593875127</v>
+        <v>0.07892832271663217</v>
       </c>
       <c r="C21">
-        <v>1055.113492643379</v>
+        <v>1046.402069952859</v>
       </c>
       <c r="D21">
-        <v>1265.817492643379</v>
+        <v>1270.122069952859</v>
       </c>
       <c r="E21">
-        <v>-324.296</v>
+        <v>-311.28</v>
       </c>
       <c r="F21">
-        <v>247.304</v>
+        <v>260.32</v>
       </c>
       <c r="G21">
         <v>36.6</v>
@@ -3009,28 +3009,28 @@
         <v>230.3</v>
       </c>
       <c r="M21">
-        <v>12.4393912</v>
+        <v>13.094096</v>
       </c>
       <c r="N21">
-        <v>217.8606088</v>
+        <v>217.205904</v>
       </c>
       <c r="O21">
-        <v>64.268879596</v>
+        <v>64.07574167999999</v>
       </c>
       <c r="P21">
-        <v>153.591729204</v>
+        <v>153.13016232</v>
       </c>
       <c r="Q21">
-        <v>189.691729204</v>
+        <v>189.23016232</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08938809992438428</v>
+        <v>0.08979502839579021</v>
       </c>
       <c r="T21">
-        <v>0.6742940431532858</v>
+        <v>0.6805890971871735</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.51376777988943</v>
+        <v>17.58807939089495</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07892832271663217</v>
+        <v>0.07871459949451309</v>
       </c>
       <c r="C22">
-        <v>1046.402069952859</v>
+        <v>1037.720023712771</v>
       </c>
       <c r="D22">
-        <v>1270.122069952859</v>
+        <v>1274.456023712771</v>
       </c>
       <c r="E22">
-        <v>-311.28</v>
+        <v>-298.264</v>
       </c>
       <c r="F22">
-        <v>260.32</v>
+        <v>273.336</v>
       </c>
       <c r="G22">
         <v>36.6</v>
@@ -3091,28 +3091,28 @@
         <v>230.3</v>
       </c>
       <c r="M22">
-        <v>13.094096</v>
+        <v>13.7488008</v>
       </c>
       <c r="N22">
-        <v>217.205904</v>
+        <v>216.5511992</v>
       </c>
       <c r="O22">
-        <v>64.07574167999999</v>
+        <v>63.882603764</v>
       </c>
       <c r="P22">
-        <v>153.13016232</v>
+        <v>152.668595436</v>
       </c>
       <c r="Q22">
-        <v>189.23016232</v>
+        <v>188.768595436</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08979502839579021</v>
+        <v>0.09021225885381404</v>
       </c>
       <c r="T22">
-        <v>0.6805890971871735</v>
+        <v>0.6870435196776155</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.58807939089495</v>
+        <v>16.75055180085234</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07871459949451309</v>
+        <v>0.07850087627239401</v>
       </c>
       <c r="C23">
-        <v>1037.720023712771</v>
+        <v>1029.067655670721</v>
       </c>
       <c r="D23">
-        <v>1274.456023712771</v>
+        <v>1278.819655670721</v>
       </c>
       <c r="E23">
-        <v>-298.2640000000001</v>
+        <v>-285.248</v>
       </c>
       <c r="F23">
-        <v>273.336</v>
+        <v>286.352</v>
       </c>
       <c r="G23">
         <v>36.6</v>
@@ -3173,28 +3173,28 @@
         <v>230.3</v>
       </c>
       <c r="M23">
-        <v>13.7488008</v>
+        <v>14.4035056</v>
       </c>
       <c r="N23">
-        <v>216.5511992</v>
+        <v>215.8964944</v>
       </c>
       <c r="O23">
-        <v>63.882603764</v>
+        <v>63.689465848</v>
       </c>
       <c r="P23">
-        <v>152.668595436</v>
+        <v>152.207028552</v>
       </c>
       <c r="Q23">
-        <v>188.768595436</v>
+        <v>188.307028552</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09021225885381404</v>
+        <v>0.09064018752871025</v>
       </c>
       <c r="T23">
-        <v>0.6870435196776155</v>
+        <v>0.6936634401806328</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.75055180085234</v>
+        <v>15.98916308263178</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07850087627239401</v>
+        <v>0.07828715305027491</v>
       </c>
       <c r="C24">
-        <v>1029.067655670721</v>
+        <v>1020.445271721148</v>
       </c>
       <c r="D24">
-        <v>1278.819655670721</v>
+        <v>1283.213271721148</v>
       </c>
       <c r="E24">
-        <v>-285.248</v>
+        <v>-272.232</v>
       </c>
       <c r="F24">
-        <v>286.352</v>
+        <v>299.368</v>
       </c>
       <c r="G24">
         <v>36.6</v>
@@ -3255,28 +3255,28 @@
         <v>230.3</v>
       </c>
       <c r="M24">
-        <v>14.4035056</v>
+        <v>15.0582104</v>
       </c>
       <c r="N24">
-        <v>215.8964944</v>
+        <v>215.2417896</v>
       </c>
       <c r="O24">
-        <v>63.689465848</v>
+        <v>63.496327932</v>
       </c>
       <c r="P24">
-        <v>152.207028552</v>
+        <v>151.745461668</v>
       </c>
       <c r="Q24">
-        <v>188.307028552</v>
+        <v>187.845461668</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09064018752871025</v>
+        <v>0.09107923123412325</v>
       </c>
       <c r="T24">
-        <v>0.6936634401806328</v>
+        <v>0.7004553066707414</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.98916308263178</v>
+        <v>15.29398207903909</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07828715305027491</v>
+        <v>0.07807342982815582</v>
       </c>
       <c r="C25">
-        <v>1020.445271721148</v>
+        <v>1011.853181976807</v>
       </c>
       <c r="D25">
-        <v>1283.213271721148</v>
+        <v>1287.637181976807</v>
       </c>
       <c r="E25">
-        <v>-272.232</v>
+        <v>-259.216</v>
       </c>
       <c r="F25">
-        <v>299.368</v>
+        <v>312.384</v>
       </c>
       <c r="G25">
         <v>36.6</v>
@@ -3337,28 +3337,28 @@
         <v>230.3</v>
       </c>
       <c r="M25">
-        <v>15.0582104</v>
+        <v>15.7129152</v>
       </c>
       <c r="N25">
-        <v>215.2417896</v>
+        <v>214.5870848</v>
       </c>
       <c r="O25">
-        <v>63.496327932</v>
+        <v>63.303190016</v>
       </c>
       <c r="P25">
-        <v>151.745461668</v>
+        <v>151.283894784</v>
       </c>
       <c r="Q25">
-        <v>187.845461668</v>
+        <v>187.383894784</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09107923123412325</v>
+        <v>0.09152982872125764</v>
       </c>
       <c r="T25">
-        <v>0.7004553066707414</v>
+        <v>0.7074259064895372</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.29398207903909</v>
+        <v>14.65673282574579</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07807342982815582</v>
+        <v>0.07785970660603672</v>
       </c>
       <c r="C26">
-        <v>1011.853181976807</v>
+        <v>1003.291700841734</v>
       </c>
       <c r="D26">
-        <v>1287.637181976807</v>
+        <v>1292.091700841734</v>
       </c>
       <c r="E26">
-        <v>-259.2160000000001</v>
+        <v>-246.2</v>
       </c>
       <c r="F26">
-        <v>312.384</v>
+        <v>325.4</v>
       </c>
       <c r="G26">
         <v>36.6</v>
@@ -3419,28 +3419,28 @@
         <v>230.3</v>
       </c>
       <c r="M26">
-        <v>15.7129152</v>
+        <v>16.36762</v>
       </c>
       <c r="N26">
-        <v>214.5870848</v>
+        <v>213.93238</v>
       </c>
       <c r="O26">
-        <v>63.303190016</v>
+        <v>63.1100521</v>
       </c>
       <c r="P26">
-        <v>151.283894784</v>
+        <v>150.8223279</v>
       </c>
       <c r="Q26">
-        <v>187.383894784</v>
+        <v>186.9223279</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09152982872125764</v>
+        <v>0.0919924421413823</v>
       </c>
       <c r="T26">
-        <v>0.7074259064895372</v>
+        <v>0.7145823889701675</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.6567328257458</v>
+        <v>14.07046351271596</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07785970660603672</v>
+        <v>0.07764598338391764</v>
       </c>
       <c r="C27">
-        <v>1003.291700841734</v>
+        <v>994.761147085728</v>
       </c>
       <c r="D27">
-        <v>1292.091700841734</v>
+        <v>1296.577147085728</v>
       </c>
       <c r="E27">
-        <v>-246.2</v>
+        <v>-233.184</v>
       </c>
       <c r="F27">
-        <v>325.4</v>
+        <v>338.416</v>
       </c>
       <c r="G27">
         <v>36.6</v>
@@ -3501,28 +3501,28 @@
         <v>230.3</v>
       </c>
       <c r="M27">
-        <v>16.36762</v>
+        <v>17.0223248</v>
       </c>
       <c r="N27">
-        <v>213.93238</v>
+        <v>213.2776752</v>
       </c>
       <c r="O27">
-        <v>63.1100521</v>
+        <v>62.916914184</v>
       </c>
       <c r="P27">
-        <v>150.8223279</v>
+        <v>150.360761016</v>
       </c>
       <c r="Q27">
-        <v>186.9223279</v>
+        <v>186.460761016</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0919924421413823</v>
+        <v>0.09246755862691572</v>
       </c>
       <c r="T27">
-        <v>0.7145823889701675</v>
+        <v>0.7219322898962202</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.07046351271596</v>
+        <v>13.52929183914996</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07764598338391764</v>
+        <v>0.07743226016179854</v>
       </c>
       <c r="C28">
-        <v>994.761147085728</v>
+        <v>986.2618439203998</v>
       </c>
       <c r="D28">
-        <v>1296.577147085728</v>
+        <v>1301.0938439204</v>
       </c>
       <c r="E28">
-        <v>-233.184</v>
+        <v>-220.168</v>
       </c>
       <c r="F28">
-        <v>338.416</v>
+        <v>351.432</v>
       </c>
       <c r="G28">
         <v>36.6</v>
@@ -3583,28 +3583,28 @@
         <v>230.3</v>
       </c>
       <c r="M28">
-        <v>17.0223248</v>
+        <v>17.6770296</v>
       </c>
       <c r="N28">
-        <v>213.2776752</v>
+        <v>212.6229704</v>
       </c>
       <c r="O28">
-        <v>62.916914184</v>
+        <v>62.723776268</v>
       </c>
       <c r="P28">
-        <v>150.360761016</v>
+        <v>149.899194132</v>
       </c>
       <c r="Q28">
-        <v>186.460761016</v>
+        <v>185.999194132</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09246755862691572</v>
+        <v>0.09295569200246374</v>
       </c>
       <c r="T28">
-        <v>0.7219322898962202</v>
+        <v>0.7294835579709318</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.52929183914996</v>
+        <v>13.02820695621848</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07743226016179854</v>
+        <v>0.07751463693967943</v>
       </c>
       <c r="C29">
-        <v>986.2618439203998</v>
+        <v>971.5012210685779</v>
       </c>
       <c r="D29">
-        <v>1301.0938439204</v>
+        <v>1299.349221068578</v>
       </c>
       <c r="E29">
-        <v>-220.168</v>
+        <v>-207.152</v>
       </c>
       <c r="F29">
-        <v>351.432</v>
+        <v>364.448</v>
       </c>
       <c r="G29">
         <v>36.6</v>
@@ -3665,45 +3665,45 @@
         <v>230.3</v>
       </c>
       <c r="M29">
-        <v>17.6770296</v>
+        <v>18.8784064</v>
       </c>
       <c r="N29">
-        <v>212.6229704</v>
+        <v>211.4215936</v>
       </c>
       <c r="O29">
-        <v>62.723776268</v>
+        <v>62.36937011199999</v>
       </c>
       <c r="P29">
-        <v>149.899194132</v>
+        <v>149.052223488</v>
       </c>
       <c r="Q29">
-        <v>185.999194132</v>
+        <v>185.152223488</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09295569200246374</v>
+        <v>0.09345738463844366</v>
       </c>
       <c r="T29">
-        <v>0.7294835579709318</v>
+        <v>0.7372445834921633</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.295</v>
       </c>
       <c r="W29">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>13.02820695621848</v>
+        <v>12.19912290901842</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07751463693967943</v>
+        <v>0.07731148871756034</v>
       </c>
       <c r="C30">
-        <v>971.5012210685779</v>
+        <v>962.7960970857541</v>
       </c>
       <c r="D30">
-        <v>1299.349221068578</v>
+        <v>1303.660097085754</v>
       </c>
       <c r="E30">
-        <v>-207.152</v>
+        <v>-194.136</v>
       </c>
       <c r="F30">
-        <v>364.448</v>
+        <v>377.464</v>
       </c>
       <c r="G30">
         <v>36.6</v>
@@ -3747,28 +3747,28 @@
         <v>230.3</v>
       </c>
       <c r="M30">
-        <v>18.8784064</v>
+        <v>19.5526352</v>
       </c>
       <c r="N30">
-        <v>211.4215936</v>
+        <v>210.7473648</v>
       </c>
       <c r="O30">
-        <v>62.36937011199999</v>
+        <v>62.170472616</v>
       </c>
       <c r="P30">
-        <v>149.052223488</v>
+        <v>148.576892184</v>
       </c>
       <c r="Q30">
-        <v>185.152223488</v>
+        <v>184.676892184</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09345738463844366</v>
+        <v>0.09397320946135261</v>
       </c>
       <c r="T30">
-        <v>0.7372445834921633</v>
+        <v>0.7452242294506125</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.19912290901842</v>
+        <v>11.77846349836262</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07731148871756034</v>
+        <v>0.07710834049544125</v>
       </c>
       <c r="C31">
-        <v>962.7960970857541</v>
+        <v>954.1196728740317</v>
       </c>
       <c r="D31">
-        <v>1303.660097085754</v>
+        <v>1307.999672874032</v>
       </c>
       <c r="E31">
-        <v>-194.1360000000001</v>
+        <v>-181.1200000000001</v>
       </c>
       <c r="F31">
-        <v>377.4639999999999</v>
+        <v>390.48</v>
       </c>
       <c r="G31">
         <v>36.6</v>
@@ -3829,28 +3829,28 @@
         <v>230.3</v>
       </c>
       <c r="M31">
-        <v>19.5526352</v>
+        <v>20.226864</v>
       </c>
       <c r="N31">
-        <v>210.7473648</v>
+        <v>210.073136</v>
       </c>
       <c r="O31">
-        <v>62.170472616</v>
+        <v>61.97157512</v>
       </c>
       <c r="P31">
-        <v>148.576892184</v>
+        <v>148.10156088</v>
       </c>
       <c r="Q31">
-        <v>184.676892184</v>
+        <v>184.20156088</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09397320946135261</v>
+        <v>0.09450377213634466</v>
       </c>
       <c r="T31">
-        <v>0.7452242294506125</v>
+        <v>0.7534318652935889</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.77846349836262</v>
+        <v>11.38584804841719</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07710834049544125</v>
+        <v>0.07690519227332215</v>
       </c>
       <c r="C32">
-        <v>954.1196728740317</v>
+        <v>945.4722359948631</v>
       </c>
       <c r="D32">
-        <v>1307.999672874032</v>
+        <v>1312.368235994863</v>
       </c>
       <c r="E32">
-        <v>-181.1200000000001</v>
+        <v>-168.104</v>
       </c>
       <c r="F32">
-        <v>390.48</v>
+        <v>403.496</v>
       </c>
       <c r="G32">
         <v>36.6</v>
@@ -3911,28 +3911,28 @@
         <v>230.3</v>
       </c>
       <c r="M32">
-        <v>20.226864</v>
+        <v>20.9010928</v>
       </c>
       <c r="N32">
-        <v>210.073136</v>
+        <v>209.3989072</v>
       </c>
       <c r="O32">
-        <v>61.97157512</v>
+        <v>61.772677624</v>
       </c>
       <c r="P32">
-        <v>148.10156088</v>
+        <v>147.626229576</v>
       </c>
       <c r="Q32">
-        <v>184.20156088</v>
+        <v>183.726229576</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09450377213634466</v>
+        <v>0.09504971343959734</v>
       </c>
       <c r="T32">
-        <v>0.7534318652935889</v>
+        <v>0.7618774036247674</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.38584804841719</v>
+        <v>11.01856262750051</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07690519227332215</v>
+        <v>0.07670204405120307</v>
       </c>
       <c r="C33">
-        <v>945.4722359948631</v>
+        <v>936.8540778642575</v>
       </c>
       <c r="D33">
-        <v>1312.368235994863</v>
+        <v>1316.766077864258</v>
       </c>
       <c r="E33">
-        <v>-168.104</v>
+        <v>-155.088</v>
       </c>
       <c r="F33">
-        <v>403.496</v>
+        <v>416.512</v>
       </c>
       <c r="G33">
         <v>36.6</v>
@@ -3993,28 +3993,28 @@
         <v>230.3</v>
       </c>
       <c r="M33">
-        <v>20.9010928</v>
+        <v>21.5753216</v>
       </c>
       <c r="N33">
-        <v>209.3989072</v>
+        <v>208.7246784</v>
       </c>
       <c r="O33">
-        <v>61.772677624</v>
+        <v>61.573780128</v>
       </c>
       <c r="P33">
-        <v>147.626229576</v>
+        <v>147.150898272</v>
       </c>
       <c r="Q33">
-        <v>183.726229576</v>
+        <v>183.250898272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09504971343959734</v>
+        <v>0.09561171184000453</v>
       </c>
       <c r="T33">
-        <v>0.7618774036247674</v>
+        <v>0.7705713401421571</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.01856262750051</v>
+        <v>10.67423254539112</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07670204405120307</v>
+        <v>0.07649889582908398</v>
       </c>
       <c r="C34">
-        <v>936.8540778642575</v>
+        <v>928.2654938175833</v>
       </c>
       <c r="D34">
-        <v>1316.766077864258</v>
+        <v>1321.193493817583</v>
       </c>
       <c r="E34">
-        <v>-155.088</v>
+        <v>-142.0720000000001</v>
       </c>
       <c r="F34">
-        <v>416.512</v>
+        <v>429.528</v>
       </c>
       <c r="G34">
         <v>36.6</v>
@@ -4075,28 +4075,28 @@
         <v>230.3</v>
       </c>
       <c r="M34">
-        <v>21.5753216</v>
+        <v>22.2495504</v>
       </c>
       <c r="N34">
-        <v>208.7246784</v>
+        <v>208.0504496</v>
       </c>
       <c r="O34">
-        <v>61.573780128</v>
+        <v>61.374882632</v>
       </c>
       <c r="P34">
-        <v>147.150898272</v>
+        <v>146.675566968</v>
       </c>
       <c r="Q34">
-        <v>183.250898272</v>
+        <v>182.775566968</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09561171184000453</v>
+        <v>0.09619048631206564</v>
       </c>
       <c r="T34">
-        <v>0.7705713401421571</v>
+        <v>0.7795247971526033</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.67423254539112</v>
+        <v>10.35077095310654</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07649889582908398</v>
+        <v>0.07629574760696489</v>
       </c>
       <c r="C35">
-        <v>928.2654938175833</v>
+        <v>919.7067831756832</v>
       </c>
       <c r="D35">
-        <v>1321.193493817583</v>
+        <v>1325.650783175683</v>
       </c>
       <c r="E35">
-        <v>-142.0720000000001</v>
+        <v>-129.056</v>
       </c>
       <c r="F35">
-        <v>429.528</v>
+        <v>442.544</v>
       </c>
       <c r="G35">
         <v>36.6</v>
@@ -4157,28 +4157,28 @@
         <v>230.3</v>
       </c>
       <c r="M35">
-        <v>22.2495504</v>
+        <v>22.9237792</v>
       </c>
       <c r="N35">
-        <v>208.0504496</v>
+        <v>207.3762208</v>
       </c>
       <c r="O35">
-        <v>61.374882632</v>
+        <v>61.17598513599999</v>
       </c>
       <c r="P35">
-        <v>146.675566968</v>
+        <v>146.200235664</v>
       </c>
       <c r="Q35">
-        <v>182.775566968</v>
+        <v>182.300235664</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09619048631206564</v>
+        <v>0.09678679940449227</v>
       </c>
       <c r="T35">
-        <v>0.7795247971526033</v>
+        <v>0.7887495710421538</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.35077095310654</v>
+        <v>10.04633651330929</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07629574760696489</v>
+        <v>0.07651207438484581</v>
       </c>
       <c r="C36">
-        <v>919.7067831756832</v>
+        <v>901.9453772736774</v>
       </c>
       <c r="D36">
-        <v>1325.650783175683</v>
+        <v>1320.905377273677</v>
       </c>
       <c r="E36">
-        <v>-129.056</v>
+        <v>-116.04</v>
       </c>
       <c r="F36">
-        <v>442.544</v>
+        <v>455.56</v>
       </c>
       <c r="G36">
         <v>36.6</v>
@@ -4239,45 +4239,45 @@
         <v>230.3</v>
       </c>
       <c r="M36">
-        <v>22.9237792</v>
+        <v>24.37246</v>
       </c>
       <c r="N36">
-        <v>207.3762208</v>
+        <v>205.92754</v>
       </c>
       <c r="O36">
-        <v>61.17598513599999</v>
+        <v>60.7486243</v>
       </c>
       <c r="P36">
-        <v>146.200235664</v>
+        <v>145.1789157</v>
       </c>
       <c r="Q36">
-        <v>182.300235664</v>
+        <v>181.2789157</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09678679940449227</v>
+        <v>0.09740146059207047</v>
       </c>
       <c r="T36">
-        <v>0.7887495710421538</v>
+        <v>0.798258184128306</v>
       </c>
       <c r="U36">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V36">
         <v>0.295</v>
       </c>
       <c r="W36">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>10.04633651330929</v>
+        <v>9.449189782237822</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07651207438484581</v>
+        <v>0.0763209111627267</v>
       </c>
       <c r="C37">
-        <v>901.9453772736774</v>
+        <v>893.1210365809636</v>
       </c>
       <c r="D37">
-        <v>1320.905377273677</v>
+        <v>1325.097036580964</v>
       </c>
       <c r="E37">
-        <v>-116.04</v>
+        <v>-103.024</v>
       </c>
       <c r="F37">
-        <v>455.56</v>
+        <v>468.576</v>
       </c>
       <c r="G37">
         <v>36.6</v>
@@ -4321,28 +4321,28 @@
         <v>230.3</v>
       </c>
       <c r="M37">
-        <v>24.37246</v>
+        <v>25.068816</v>
       </c>
       <c r="N37">
-        <v>205.92754</v>
+        <v>205.231184</v>
       </c>
       <c r="O37">
-        <v>60.7486243</v>
+        <v>60.54319928</v>
       </c>
       <c r="P37">
-        <v>145.1789157</v>
+        <v>144.68798472</v>
       </c>
       <c r="Q37">
-        <v>181.2789157</v>
+        <v>180.78798472</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09740146059207047</v>
+        <v>0.09803532994176048</v>
       </c>
       <c r="T37">
-        <v>0.798258184128306</v>
+        <v>0.8080639413734003</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.449189782237822</v>
+        <v>9.18671228828677</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07632091116272671</v>
+        <v>0.07612974794060762</v>
       </c>
       <c r="C38">
-        <v>893.1210365809634</v>
+        <v>884.3233835539255</v>
       </c>
       <c r="D38">
-        <v>1325.097036580964</v>
+        <v>1329.315383553926</v>
       </c>
       <c r="E38">
-        <v>-103.0240000000001</v>
+        <v>-90.00800000000004</v>
       </c>
       <c r="F38">
-        <v>468.576</v>
+        <v>481.592</v>
       </c>
       <c r="G38">
         <v>36.6</v>
@@ -4403,28 +4403,28 @@
         <v>230.3</v>
       </c>
       <c r="M38">
-        <v>25.068816</v>
+        <v>25.765172</v>
       </c>
       <c r="N38">
-        <v>205.231184</v>
+        <v>204.534828</v>
       </c>
       <c r="O38">
-        <v>60.54319928</v>
+        <v>60.33777426</v>
       </c>
       <c r="P38">
-        <v>144.68798472</v>
+        <v>144.19705374</v>
       </c>
       <c r="Q38">
-        <v>180.78798472</v>
+        <v>180.29705374</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09803532994176048</v>
+        <v>0.09868932212794859</v>
       </c>
       <c r="T38">
-        <v>0.8080639413734002</v>
+        <v>0.8181809924992912</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.186712288286772</v>
+        <v>8.938422766981724</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07612974794060762</v>
+        <v>0.07593858471848852</v>
       </c>
       <c r="C39">
-        <v>884.3233835539255</v>
+        <v>875.5526738810725</v>
       </c>
       <c r="D39">
-        <v>1329.315383553926</v>
+        <v>1333.560673881072</v>
       </c>
       <c r="E39">
-        <v>-90.00800000000004</v>
+        <v>-76.99200000000008</v>
       </c>
       <c r="F39">
-        <v>481.592</v>
+        <v>494.6079999999999</v>
       </c>
       <c r="G39">
         <v>36.6</v>
@@ -4485,28 +4485,28 @@
         <v>230.3</v>
       </c>
       <c r="M39">
-        <v>25.765172</v>
+        <v>26.461528</v>
       </c>
       <c r="N39">
-        <v>204.534828</v>
+        <v>203.838472</v>
       </c>
       <c r="O39">
-        <v>60.33777426</v>
+        <v>60.13234924</v>
       </c>
       <c r="P39">
-        <v>144.19705374</v>
+        <v>143.70612276</v>
       </c>
       <c r="Q39">
-        <v>180.29705374</v>
+        <v>179.80612276</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09868932212794859</v>
+        <v>0.09936441083627182</v>
       </c>
       <c r="T39">
-        <v>0.8181809924992912</v>
+        <v>0.8286244001131143</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.938422766981724</v>
+        <v>8.703201115219047</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07593858471848852</v>
+        <v>0.07574742149636943</v>
       </c>
       <c r="C40">
-        <v>875.5526738810725</v>
+        <v>866.8091665276343</v>
       </c>
       <c r="D40">
-        <v>1333.560673881072</v>
+        <v>1337.833166527634</v>
       </c>
       <c r="E40">
-        <v>-76.99200000000008</v>
+        <v>-63.97600000000006</v>
       </c>
       <c r="F40">
-        <v>494.6079999999999</v>
+        <v>507.624</v>
       </c>
       <c r="G40">
         <v>36.6</v>
@@ -4567,28 +4567,28 @@
         <v>230.3</v>
       </c>
       <c r="M40">
-        <v>26.461528</v>
+        <v>27.157884</v>
       </c>
       <c r="N40">
-        <v>203.838472</v>
+        <v>203.142116</v>
       </c>
       <c r="O40">
-        <v>60.13234924</v>
+        <v>59.92692422</v>
       </c>
       <c r="P40">
-        <v>143.70612276</v>
+        <v>143.21519178</v>
       </c>
       <c r="Q40">
-        <v>179.80612276</v>
+        <v>179.31519178</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09936441083627182</v>
+        <v>0.1000616336006056</v>
       </c>
       <c r="T40">
-        <v>0.8286244001131143</v>
+        <v>0.8394102145339479</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.703201115219047</v>
+        <v>8.480042112264712</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07574742149636943</v>
+        <v>0.07555625827425035</v>
       </c>
       <c r="C41">
-        <v>866.8091665276343</v>
+        <v>858.0931237882243</v>
       </c>
       <c r="D41">
-        <v>1337.833166527634</v>
+        <v>1342.133123788224</v>
       </c>
       <c r="E41">
-        <v>-63.97600000000006</v>
+        <v>-50.96000000000004</v>
       </c>
       <c r="F41">
-        <v>507.624</v>
+        <v>520.64</v>
       </c>
       <c r="G41">
         <v>36.6</v>
@@ -4649,28 +4649,28 @@
         <v>230.3</v>
       </c>
       <c r="M41">
-        <v>27.157884</v>
+        <v>27.85424</v>
       </c>
       <c r="N41">
-        <v>203.142116</v>
+        <v>202.44576</v>
       </c>
       <c r="O41">
-        <v>59.92692422</v>
+        <v>59.7214992</v>
       </c>
       <c r="P41">
-        <v>143.21519178</v>
+        <v>142.7242608</v>
       </c>
       <c r="Q41">
-        <v>179.31519178</v>
+        <v>178.8242608</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1000616336006056</v>
+        <v>0.1007820971237506</v>
       </c>
       <c r="T41">
-        <v>0.8394102145339479</v>
+        <v>0.8505555561021426</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.480042112264712</v>
+        <v>8.268041059458096</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07555625827425035</v>
+        <v>0.07536509505213125</v>
       </c>
       <c r="C42">
-        <v>858.0931237882243</v>
+        <v>849.4048113405152</v>
       </c>
       <c r="D42">
-        <v>1342.133123788224</v>
+        <v>1346.460811340515</v>
       </c>
       <c r="E42">
-        <v>-50.96000000000004</v>
+        <v>-37.94400000000007</v>
       </c>
       <c r="F42">
-        <v>520.64</v>
+        <v>533.6559999999999</v>
       </c>
       <c r="G42">
         <v>36.6</v>
@@ -4731,28 +4731,28 @@
         <v>230.3</v>
       </c>
       <c r="M42">
-        <v>27.85424</v>
+        <v>28.550596</v>
       </c>
       <c r="N42">
-        <v>202.44576</v>
+        <v>201.749404</v>
       </c>
       <c r="O42">
-        <v>59.7214992</v>
+        <v>59.51607418</v>
       </c>
       <c r="P42">
-        <v>142.7242608</v>
+        <v>142.23332982</v>
       </c>
       <c r="Q42">
-        <v>178.8242608</v>
+        <v>178.33332982</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1007820971237506</v>
+        <v>0.1015269831392055</v>
       </c>
       <c r="T42">
-        <v>0.8505555561021426</v>
+        <v>0.8620787058590896</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.268041059458096</v>
+        <v>8.066381521422532</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07536509505213125</v>
+        <v>0.07517393183001216</v>
       </c>
       <c r="C43">
-        <v>849.4048113405152</v>
+        <v>840.7444982999589</v>
       </c>
       <c r="D43">
-        <v>1346.460811340515</v>
+        <v>1350.816498299959</v>
       </c>
       <c r="E43">
-        <v>-37.94400000000007</v>
+        <v>-24.928</v>
       </c>
       <c r="F43">
-        <v>533.6559999999999</v>
+        <v>546.672</v>
       </c>
       <c r="G43">
         <v>36.6</v>
@@ -4813,28 +4813,28 @@
         <v>230.3</v>
       </c>
       <c r="M43">
-        <v>28.550596</v>
+        <v>29.246952</v>
       </c>
       <c r="N43">
-        <v>201.749404</v>
+        <v>201.053048</v>
       </c>
       <c r="O43">
-        <v>59.51607418</v>
+        <v>59.31064916</v>
       </c>
       <c r="P43">
-        <v>142.23332982</v>
+        <v>141.74239884</v>
       </c>
       <c r="Q43">
-        <v>178.33332982</v>
+        <v>177.84239884</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1015269831392055</v>
+        <v>0.1022975548793313</v>
       </c>
       <c r="T43">
-        <v>0.8620787058590896</v>
+        <v>0.8739992056076555</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.066381521422532</v>
+        <v>7.874324818531518</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07517393183001217</v>
+        <v>0.07498276860789309</v>
       </c>
       <c r="C44">
-        <v>840.7444982999588</v>
+        <v>832.1124572755715</v>
       </c>
       <c r="D44">
-        <v>1350.816498299959</v>
+        <v>1355.200457275572</v>
       </c>
       <c r="E44">
-        <v>-24.92800000000011</v>
+        <v>-11.91200000000003</v>
       </c>
       <c r="F44">
-        <v>546.6719999999999</v>
+        <v>559.688</v>
       </c>
       <c r="G44">
         <v>36.6</v>
@@ -4895,28 +4895,28 @@
         <v>230.3</v>
       </c>
       <c r="M44">
-        <v>29.24695199999999</v>
+        <v>29.943308</v>
       </c>
       <c r="N44">
-        <v>201.053048</v>
+        <v>200.356692</v>
       </c>
       <c r="O44">
-        <v>59.31064916</v>
+        <v>59.10522414</v>
       </c>
       <c r="P44">
-        <v>141.74239884</v>
+        <v>141.25146786</v>
       </c>
       <c r="Q44">
-        <v>177.84239884</v>
+        <v>177.35146786</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1022975548793313</v>
+        <v>0.1030951642243738</v>
       </c>
       <c r="T44">
-        <v>0.8739992056076555</v>
+        <v>0.8863379685052939</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.87432481853152</v>
+        <v>7.691200985542413</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07498276860789309</v>
+        <v>0.075039765385774</v>
       </c>
       <c r="C45">
-        <v>832.1124572755715</v>
+        <v>817.7863719325239</v>
       </c>
       <c r="D45">
-        <v>1355.200457275572</v>
+        <v>1353.890371932524</v>
       </c>
       <c r="E45">
-        <v>-11.91200000000003</v>
+        <v>1.103999999999928</v>
       </c>
       <c r="F45">
-        <v>559.688</v>
+        <v>572.704</v>
       </c>
       <c r="G45">
         <v>36.6</v>
@@ -4977,45 +4977,45 @@
         <v>230.3</v>
       </c>
       <c r="M45">
-        <v>29.943308</v>
+        <v>31.0978272</v>
       </c>
       <c r="N45">
-        <v>200.356692</v>
+        <v>199.2021728</v>
       </c>
       <c r="O45">
-        <v>59.10522414</v>
+        <v>58.764640976</v>
       </c>
       <c r="P45">
-        <v>141.25146786</v>
+        <v>140.437531824</v>
       </c>
       <c r="Q45">
-        <v>177.35146786</v>
+        <v>176.537531824</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1030951642243738</v>
+        <v>0.1039212596174535</v>
       </c>
       <c r="T45">
-        <v>0.8863379685052939</v>
+        <v>0.8991174015064194</v>
       </c>
       <c r="U45">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V45">
         <v>0.295</v>
       </c>
       <c r="W45">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y45">
-        <v>7.691200985542413</v>
+        <v>7.405662090758548</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.075039765385774</v>
+        <v>0.07485424216365488</v>
       </c>
       <c r="C46">
-        <v>817.7863719325239</v>
+        <v>809.0439951976</v>
       </c>
       <c r="D46">
-        <v>1353.890371932524</v>
+        <v>1358.1639951976</v>
       </c>
       <c r="E46">
-        <v>1.103999999999928</v>
+        <v>14.12</v>
       </c>
       <c r="F46">
-        <v>572.704</v>
+        <v>585.72</v>
       </c>
       <c r="G46">
         <v>36.6</v>
@@ -5059,28 +5059,28 @@
         <v>230.3</v>
       </c>
       <c r="M46">
-        <v>31.0978272</v>
+        <v>31.804596</v>
       </c>
       <c r="N46">
-        <v>199.2021728</v>
+        <v>198.495404</v>
       </c>
       <c r="O46">
-        <v>58.764640976</v>
+        <v>58.55614418</v>
       </c>
       <c r="P46">
-        <v>140.437531824</v>
+        <v>139.93925982</v>
       </c>
       <c r="Q46">
-        <v>176.537531824</v>
+        <v>176.03925982</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1039212596174535</v>
+        <v>0.1047773948430089</v>
       </c>
       <c r="T46">
-        <v>0.8991174015064194</v>
+        <v>0.9123615411621312</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.405662090758548</v>
+        <v>7.241091822075023</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07485424216365488</v>
+        <v>0.0746687189415358</v>
       </c>
       <c r="C47">
-        <v>809.0439951976</v>
+        <v>800.3286837103907</v>
       </c>
       <c r="D47">
-        <v>1358.1639951976</v>
+        <v>1362.464683710391</v>
       </c>
       <c r="E47">
-        <v>14.12</v>
+        <v>27.13599999999997</v>
       </c>
       <c r="F47">
-        <v>585.72</v>
+        <v>598.736</v>
       </c>
       <c r="G47">
         <v>36.6</v>
@@ -5141,28 +5141,28 @@
         <v>230.3</v>
       </c>
       <c r="M47">
-        <v>31.804596</v>
+        <v>32.5113648</v>
       </c>
       <c r="N47">
-        <v>198.495404</v>
+        <v>197.7886352</v>
       </c>
       <c r="O47">
-        <v>58.55614418</v>
+        <v>58.347647384</v>
       </c>
       <c r="P47">
-        <v>139.93925982</v>
+        <v>139.440987816</v>
       </c>
       <c r="Q47">
-        <v>176.03925982</v>
+        <v>175.540987816</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1047773948430089</v>
+        <v>0.1056652387806219</v>
       </c>
       <c r="T47">
-        <v>0.9123615411621312</v>
+        <v>0.9260962045087955</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.241091822075023</v>
+        <v>7.083676782464697</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0746687189415358</v>
+        <v>0.07448319571941672</v>
       </c>
       <c r="C48">
-        <v>800.3286837103907</v>
+        <v>791.6406953976743</v>
       </c>
       <c r="D48">
-        <v>1362.464683710391</v>
+        <v>1366.792695397674</v>
       </c>
       <c r="E48">
-        <v>27.13599999999997</v>
+        <v>40.15199999999993</v>
       </c>
       <c r="F48">
-        <v>598.736</v>
+        <v>611.752</v>
       </c>
       <c r="G48">
         <v>36.6</v>
@@ -5223,28 +5223,28 @@
         <v>230.3</v>
       </c>
       <c r="M48">
-        <v>32.5113648</v>
+        <v>33.2181336</v>
       </c>
       <c r="N48">
-        <v>197.7886352</v>
+        <v>197.0818664</v>
       </c>
       <c r="O48">
-        <v>58.347647384</v>
+        <v>58.13915058800001</v>
       </c>
       <c r="P48">
-        <v>139.440987816</v>
+        <v>138.942715812</v>
       </c>
       <c r="Q48">
-        <v>175.540987816</v>
+        <v>175.042715812</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1056652387806219</v>
+        <v>0.1065865862630504</v>
       </c>
       <c r="T48">
-        <v>0.9260962045087955</v>
+        <v>0.9403491570383526</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.083676782464697</v>
+        <v>6.932960255178214</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07448319571941672</v>
+        <v>0.07429767249729763</v>
       </c>
       <c r="C49">
-        <v>791.6406953976743</v>
+        <v>782.980291473998</v>
       </c>
       <c r="D49">
-        <v>1366.792695397674</v>
+        <v>1371.148291473998</v>
       </c>
       <c r="E49">
-        <v>40.15199999999993</v>
+        <v>53.16800000000001</v>
       </c>
       <c r="F49">
-        <v>611.752</v>
+        <v>624.768</v>
       </c>
       <c r="G49">
         <v>36.6</v>
@@ -5305,28 +5305,28 @@
         <v>230.3</v>
       </c>
       <c r="M49">
-        <v>33.2181336</v>
+        <v>33.9249024</v>
       </c>
       <c r="N49">
-        <v>197.0818664</v>
+        <v>196.3750976</v>
       </c>
       <c r="O49">
-        <v>58.13915058800001</v>
+        <v>57.930653792</v>
       </c>
       <c r="P49">
-        <v>138.942715812</v>
+        <v>138.444443808</v>
       </c>
       <c r="Q49">
-        <v>175.042715812</v>
+        <v>174.544443808</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1065865862630504</v>
+        <v>0.1075433701871108</v>
       </c>
       <c r="T49">
-        <v>0.9403491570383526</v>
+        <v>0.9551503000498157</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.932960255178214</v>
+        <v>6.788523583195334</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07429767249729763</v>
+        <v>0.07411214927517852</v>
       </c>
       <c r="C50">
-        <v>782.9802914739981</v>
+        <v>774.3477364942327</v>
       </c>
       <c r="D50">
-        <v>1371.148291473998</v>
+        <v>1375.531736494233</v>
       </c>
       <c r="E50">
-        <v>53.16799999999989</v>
+        <v>66.18399999999997</v>
       </c>
       <c r="F50">
-        <v>624.7679999999999</v>
+        <v>637.784</v>
       </c>
       <c r="G50">
         <v>36.6</v>
@@ -5387,28 +5387,28 @@
         <v>230.3</v>
       </c>
       <c r="M50">
-        <v>33.92490239999999</v>
+        <v>34.6316712</v>
       </c>
       <c r="N50">
-        <v>196.3750976</v>
+        <v>195.6683288</v>
       </c>
       <c r="O50">
-        <v>57.930653792</v>
+        <v>57.722156996</v>
       </c>
       <c r="P50">
-        <v>138.444443808</v>
+        <v>137.946171804</v>
       </c>
       <c r="Q50">
-        <v>174.544443808</v>
+        <v>174.046171804</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1075433701871108</v>
+        <v>0.1085376750493696</v>
       </c>
       <c r="T50">
-        <v>0.9551503000498157</v>
+        <v>0.9705318800421205</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.788523583195335</v>
+        <v>6.649982285579103</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07411214927517852</v>
+        <v>0.07392662605305943</v>
       </c>
       <c r="C51">
-        <v>774.3477364942327</v>
+        <v>765.7432984071354</v>
       </c>
       <c r="D51">
-        <v>1375.531736494233</v>
+        <v>1379.943298407135</v>
       </c>
       <c r="E51">
-        <v>66.18399999999997</v>
+        <v>79.19999999999993</v>
       </c>
       <c r="F51">
-        <v>637.784</v>
+        <v>650.8</v>
       </c>
       <c r="G51">
         <v>36.6</v>
@@ -5469,28 +5469,28 @@
         <v>230.3</v>
       </c>
       <c r="M51">
-        <v>34.6316712</v>
+        <v>35.33844</v>
       </c>
       <c r="N51">
-        <v>195.6683288</v>
+        <v>194.96156</v>
       </c>
       <c r="O51">
-        <v>57.722156996</v>
+        <v>57.5136602</v>
       </c>
       <c r="P51">
-        <v>137.946171804</v>
+        <v>137.4478998</v>
       </c>
       <c r="Q51">
-        <v>174.046171804</v>
+        <v>173.5478998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1085376750493696</v>
+        <v>0.1095717521061189</v>
       </c>
       <c r="T51">
-        <v>0.9705318800421205</v>
+        <v>0.9865287232341178</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.649982285579103</v>
+        <v>6.516982639867522</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07392662605305943</v>
+        <v>0.07374110283094033</v>
       </c>
       <c r="C52">
-        <v>765.7432984071354</v>
+        <v>757.1672486099516</v>
       </c>
       <c r="D52">
-        <v>1379.943298407135</v>
+        <v>1384.383248609952</v>
       </c>
       <c r="E52">
-        <v>79.19999999999993</v>
+        <v>92.21599999999989</v>
       </c>
       <c r="F52">
-        <v>650.8</v>
+        <v>663.8159999999999</v>
       </c>
       <c r="G52">
         <v>36.6</v>
@@ -5551,28 +5551,28 @@
         <v>230.3</v>
       </c>
       <c r="M52">
-        <v>35.33844</v>
+        <v>36.0452088</v>
       </c>
       <c r="N52">
-        <v>194.96156</v>
+        <v>194.2547912</v>
       </c>
       <c r="O52">
-        <v>57.5136602</v>
+        <v>57.305163404</v>
       </c>
       <c r="P52">
-        <v>137.4478998</v>
+        <v>136.949627796</v>
       </c>
       <c r="Q52">
-        <v>173.5478998</v>
+        <v>173.049627796</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1095717521061189</v>
+        <v>0.1106480363896742</v>
       </c>
       <c r="T52">
-        <v>0.9865287232341178</v>
+        <v>1.003178498801298</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.516982639867522</v>
+        <v>6.389198666536785</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07374110283094033</v>
+        <v>0.07355557960882125</v>
       </c>
       <c r="C53">
-        <v>757.1672486099516</v>
+        <v>748.6198620040703</v>
       </c>
       <c r="D53">
-        <v>1384.383248609952</v>
+        <v>1388.85186200407</v>
       </c>
       <c r="E53">
-        <v>92.21599999999989</v>
+        <v>105.232</v>
       </c>
       <c r="F53">
-        <v>663.8159999999999</v>
+        <v>676.832</v>
       </c>
       <c r="G53">
         <v>36.6</v>
@@ -5633,28 +5633,28 @@
         <v>230.3</v>
       </c>
       <c r="M53">
-        <v>36.0452088</v>
+        <v>36.7519776</v>
       </c>
       <c r="N53">
-        <v>194.2547912</v>
+        <v>193.5480224</v>
       </c>
       <c r="O53">
-        <v>57.305163404</v>
+        <v>57.096666608</v>
       </c>
       <c r="P53">
-        <v>136.949627796</v>
+        <v>136.451355792</v>
       </c>
       <c r="Q53">
-        <v>173.049627796</v>
+        <v>172.551355792</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1106480363896742</v>
+        <v>0.1117691658517109</v>
       </c>
       <c r="T53">
-        <v>1.003178498801298</v>
+        <v>1.020522015017111</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.389198666536785</v>
+        <v>6.266329461411078</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07355557960882125</v>
+        <v>0.07337005638670216</v>
       </c>
       <c r="C54">
-        <v>748.6198620040703</v>
+        <v>740.1014170517622</v>
       </c>
       <c r="D54">
-        <v>1388.85186200407</v>
+        <v>1393.349417051762</v>
       </c>
       <c r="E54">
-        <v>105.232</v>
+        <v>118.2479999999999</v>
       </c>
       <c r="F54">
-        <v>676.832</v>
+        <v>689.848</v>
       </c>
       <c r="G54">
         <v>36.6</v>
@@ -5715,28 +5715,28 @@
         <v>230.3</v>
       </c>
       <c r="M54">
-        <v>36.7519776</v>
+        <v>37.4587464</v>
       </c>
       <c r="N54">
-        <v>193.5480224</v>
+        <v>192.8412536</v>
       </c>
       <c r="O54">
-        <v>57.096666608</v>
+        <v>56.888169812</v>
       </c>
       <c r="P54">
-        <v>136.451355792</v>
+        <v>135.953083788</v>
       </c>
       <c r="Q54">
-        <v>172.551355792</v>
+        <v>172.053083788</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1117691658517109</v>
+        <v>0.1129380029504301</v>
       </c>
       <c r="T54">
-        <v>1.020522015017111</v>
+        <v>1.038603553199555</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.266329461411078</v>
+        <v>6.1480968300637</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07337005638670216</v>
+        <v>0.07356523316458308</v>
       </c>
       <c r="C55">
-        <v>740.1014170517622</v>
+        <v>722.3546298270981</v>
       </c>
       <c r="D55">
-        <v>1393.349417051762</v>
+        <v>1388.618629827098</v>
       </c>
       <c r="E55">
-        <v>118.2479999999999</v>
+        <v>131.264</v>
       </c>
       <c r="F55">
-        <v>689.848</v>
+        <v>702.864</v>
       </c>
       <c r="G55">
         <v>36.6</v>
@@ -5797,45 +5797,45 @@
         <v>230.3</v>
       </c>
       <c r="M55">
-        <v>37.4587464</v>
+        <v>38.8683792</v>
       </c>
       <c r="N55">
-        <v>192.8412536</v>
+        <v>191.4316208</v>
       </c>
       <c r="O55">
-        <v>56.888169812</v>
+        <v>56.472328136</v>
       </c>
       <c r="P55">
-        <v>135.953083788</v>
+        <v>134.959292664</v>
       </c>
       <c r="Q55">
-        <v>172.053083788</v>
+        <v>171.059292664</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1129380029504301</v>
+        <v>0.1141576590534415</v>
       </c>
       <c r="T55">
-        <v>1.038603553199555</v>
+        <v>1.057471245216018</v>
       </c>
       <c r="U55">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V55">
         <v>0.295</v>
       </c>
       <c r="W55">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>6.1480968300637</v>
+        <v>5.925124863451987</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07356523316458308</v>
+        <v>0.07338675994246399</v>
       </c>
       <c r="C56">
-        <v>722.3546298270981</v>
+        <v>713.6632874457301</v>
       </c>
       <c r="D56">
-        <v>1388.618629827098</v>
+        <v>1392.94328744573</v>
       </c>
       <c r="E56">
-        <v>131.264</v>
+        <v>144.28</v>
       </c>
       <c r="F56">
-        <v>702.864</v>
+        <v>715.88</v>
       </c>
       <c r="G56">
         <v>36.6</v>
@@ -5879,28 +5879,28 @@
         <v>230.3</v>
       </c>
       <c r="M56">
-        <v>38.8683792</v>
+        <v>39.588164</v>
       </c>
       <c r="N56">
-        <v>191.4316208</v>
+        <v>190.711836</v>
       </c>
       <c r="O56">
-        <v>56.472328136</v>
+        <v>56.25999162</v>
       </c>
       <c r="P56">
-        <v>134.959292664</v>
+        <v>134.45184438</v>
       </c>
       <c r="Q56">
-        <v>171.059292664</v>
+        <v>170.55184438</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1141576590534415</v>
+        <v>0.1154315220943644</v>
       </c>
       <c r="T56">
-        <v>1.057471245216018</v>
+        <v>1.077177501322101</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.925124863451987</v>
+        <v>5.817395320480132</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07338675994246399</v>
+        <v>0.07320828672034489</v>
       </c>
       <c r="C57">
-        <v>713.6632874457301</v>
+        <v>704.9989662952479</v>
       </c>
       <c r="D57">
-        <v>1392.94328744573</v>
+        <v>1397.294966295248</v>
       </c>
       <c r="E57">
-        <v>144.28</v>
+        <v>157.296</v>
       </c>
       <c r="F57">
-        <v>715.88</v>
+        <v>728.8960000000001</v>
       </c>
       <c r="G57">
         <v>36.6</v>
@@ -5961,28 +5961,28 @@
         <v>230.3</v>
       </c>
       <c r="M57">
-        <v>39.588164</v>
+        <v>40.30794880000001</v>
       </c>
       <c r="N57">
-        <v>190.711836</v>
+        <v>189.9920512</v>
       </c>
       <c r="O57">
-        <v>56.25999162</v>
+        <v>56.04765510399999</v>
       </c>
       <c r="P57">
-        <v>134.45184438</v>
+        <v>133.944396096</v>
       </c>
       <c r="Q57">
-        <v>170.55184438</v>
+        <v>170.044396096</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1154315220943644</v>
+        <v>0.1167632880007838</v>
       </c>
       <c r="T57">
-        <v>1.077177501322101</v>
+        <v>1.097779496342097</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.817395320480132</v>
+        <v>5.713513261185843</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07320828672034489</v>
+        <v>0.07302981349822581</v>
       </c>
       <c r="C58">
-        <v>704.9989662952479</v>
+        <v>696.3619204195002</v>
       </c>
       <c r="D58">
-        <v>1397.294966295248</v>
+        <v>1401.6739204195</v>
       </c>
       <c r="E58">
-        <v>157.296</v>
+        <v>170.312</v>
       </c>
       <c r="F58">
-        <v>728.8960000000001</v>
+        <v>741.912</v>
       </c>
       <c r="G58">
         <v>36.6</v>
@@ -6043,28 +6043,28 @@
         <v>230.3</v>
       </c>
       <c r="M58">
-        <v>40.30794880000001</v>
+        <v>41.0277336</v>
       </c>
       <c r="N58">
-        <v>189.9920512</v>
+        <v>189.2722664</v>
       </c>
       <c r="O58">
-        <v>56.04765510399999</v>
+        <v>55.835318588</v>
       </c>
       <c r="P58">
-        <v>133.944396096</v>
+        <v>133.436947812</v>
       </c>
       <c r="Q58">
-        <v>170.044396096</v>
+        <v>169.536947812</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1167632880007838</v>
+        <v>0.1181569965075019</v>
       </c>
       <c r="T58">
-        <v>1.097779496342097</v>
+        <v>1.119339723688605</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.713513261185843</v>
+        <v>5.613276186428196</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07302981349822581</v>
+        <v>0.07285134027610671</v>
       </c>
       <c r="C59">
-        <v>696.3619204195002</v>
+        <v>687.7524070569192</v>
       </c>
       <c r="D59">
-        <v>1401.6739204195</v>
+        <v>1406.080407056919</v>
       </c>
       <c r="E59">
-        <v>170.312</v>
+        <v>183.328</v>
       </c>
       <c r="F59">
-        <v>741.912</v>
+        <v>754.928</v>
       </c>
       <c r="G59">
         <v>36.6</v>
@@ -6125,28 +6125,28 @@
         <v>230.3</v>
       </c>
       <c r="M59">
-        <v>41.0277336</v>
+        <v>41.7475184</v>
       </c>
       <c r="N59">
-        <v>189.2722664</v>
+        <v>188.5524816</v>
       </c>
       <c r="O59">
-        <v>55.835318588</v>
+        <v>55.62298207200001</v>
       </c>
       <c r="P59">
-        <v>133.436947812</v>
+        <v>132.929499528</v>
       </c>
       <c r="Q59">
-        <v>169.536947812</v>
+        <v>169.029499528</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1181569965075019</v>
+        <v>0.1196170720859684</v>
       </c>
       <c r="T59">
-        <v>1.119339723688605</v>
+        <v>1.141926628527804</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.613276186428196</v>
+        <v>5.516495562524263</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07285134027610671</v>
+        <v>0.07267286705398762</v>
       </c>
       <c r="C60">
-        <v>687.7524070569193</v>
+        <v>679.1706866908912</v>
       </c>
       <c r="D60">
-        <v>1406.080407056919</v>
+        <v>1410.514686690891</v>
       </c>
       <c r="E60">
-        <v>183.3279999999999</v>
+        <v>196.3439999999999</v>
       </c>
       <c r="F60">
-        <v>754.9279999999999</v>
+        <v>767.944</v>
       </c>
       <c r="G60">
         <v>36.6</v>
@@ -6207,28 +6207,28 @@
         <v>230.3</v>
       </c>
       <c r="M60">
-        <v>41.7475184</v>
+        <v>42.4673032</v>
       </c>
       <c r="N60">
-        <v>188.5524816</v>
+        <v>187.8326968</v>
       </c>
       <c r="O60">
-        <v>55.62298207200001</v>
+        <v>55.410645556</v>
       </c>
       <c r="P60">
-        <v>132.929499528</v>
+        <v>132.422051244</v>
       </c>
       <c r="Q60">
-        <v>169.029499528</v>
+        <v>168.522051244</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1196170720859683</v>
+        <v>0.1211483708633844</v>
       </c>
       <c r="T60">
-        <v>1.141926628527804</v>
+        <v>1.165615333603061</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.516495562524264</v>
+        <v>5.422995637735716</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07267286705398762</v>
+        <v>0.07249439383186852</v>
       </c>
       <c r="C61">
-        <v>679.1706866908912</v>
+        <v>670.6170231010893</v>
       </c>
       <c r="D61">
-        <v>1410.514686690891</v>
+        <v>1414.977023101089</v>
       </c>
       <c r="E61">
-        <v>196.3439999999999</v>
+        <v>209.3599999999999</v>
       </c>
       <c r="F61">
-        <v>767.944</v>
+        <v>780.9599999999999</v>
       </c>
       <c r="G61">
         <v>36.6</v>
@@ -6289,28 +6289,28 @@
         <v>230.3</v>
       </c>
       <c r="M61">
-        <v>42.4673032</v>
+        <v>43.187088</v>
       </c>
       <c r="N61">
-        <v>187.8326968</v>
+        <v>187.112912</v>
       </c>
       <c r="O61">
-        <v>55.410645556</v>
+        <v>55.19830904000001</v>
       </c>
       <c r="P61">
-        <v>132.422051244</v>
+        <v>131.91460296</v>
       </c>
       <c r="Q61">
-        <v>168.522051244</v>
+        <v>168.01460296</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1211483708633844</v>
+        <v>0.1227562345796713</v>
       </c>
       <c r="T61">
-        <v>1.165615333603061</v>
+        <v>1.19048847393208</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.422995637735716</v>
+        <v>5.332612377106788</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07249439383186852</v>
+        <v>0.07231592060974944</v>
       </c>
       <c r="C62">
-        <v>670.6170231010893</v>
+        <v>662.0916834157758</v>
       </c>
       <c r="D62">
-        <v>1414.977023101089</v>
+        <v>1419.467683415776</v>
       </c>
       <c r="E62">
-        <v>209.3599999999999</v>
+        <v>222.3759999999999</v>
       </c>
       <c r="F62">
-        <v>780.9599999999999</v>
+        <v>793.9759999999999</v>
       </c>
       <c r="G62">
         <v>36.6</v>
@@ -6371,28 +6371,28 @@
         <v>230.3</v>
       </c>
       <c r="M62">
-        <v>43.187088</v>
+        <v>43.9068728</v>
       </c>
       <c r="N62">
-        <v>187.112912</v>
+        <v>186.3931272</v>
       </c>
       <c r="O62">
-        <v>55.19830904000001</v>
+        <v>54.985972524</v>
       </c>
       <c r="P62">
-        <v>131.91460296</v>
+        <v>131.407154676</v>
       </c>
       <c r="Q62">
-        <v>168.01460296</v>
+        <v>167.507154676</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1227562345796713</v>
+        <v>0.1244465528455114</v>
       </c>
       <c r="T62">
-        <v>1.19048847393208</v>
+        <v>1.216637159918999</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.332612377106788</v>
+        <v>5.245192502072251</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07231592060974944</v>
+        <v>0.07213744738763034</v>
       </c>
       <c r="C63">
-        <v>662.0916834157758</v>
+        <v>653.5949381651117</v>
       </c>
       <c r="D63">
-        <v>1419.467683415776</v>
+        <v>1423.986938165112</v>
       </c>
       <c r="E63">
-        <v>222.3759999999999</v>
+        <v>235.3919999999999</v>
       </c>
       <c r="F63">
-        <v>793.9759999999999</v>
+        <v>806.992</v>
       </c>
       <c r="G63">
         <v>36.6</v>
@@ -6453,28 +6453,28 @@
         <v>230.3</v>
       </c>
       <c r="M63">
-        <v>43.9068728</v>
+        <v>44.6266576</v>
       </c>
       <c r="N63">
-        <v>186.3931272</v>
+        <v>185.6733424</v>
       </c>
       <c r="O63">
-        <v>54.985972524</v>
+        <v>54.773636008</v>
       </c>
       <c r="P63">
-        <v>131.407154676</v>
+        <v>130.899706392</v>
       </c>
       <c r="Q63">
-        <v>167.507154676</v>
+        <v>166.999706392</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1244465528455114</v>
+        <v>0.1262258352306062</v>
       </c>
       <c r="T63">
-        <v>1.216637159918999</v>
+        <v>1.244162092536808</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.245192502072251</v>
+        <v>5.160592623006568</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07213744738763034</v>
+        <v>0.07195897416551125</v>
       </c>
       <c r="C64">
-        <v>653.5949381651117</v>
+        <v>645.1270613354799</v>
       </c>
       <c r="D64">
-        <v>1423.986938165112</v>
+        <v>1428.53506133548</v>
       </c>
       <c r="E64">
-        <v>235.3919999999999</v>
+        <v>248.4079999999999</v>
       </c>
       <c r="F64">
-        <v>806.992</v>
+        <v>820.0079999999999</v>
       </c>
       <c r="G64">
         <v>36.6</v>
@@ -6535,28 +6535,28 @@
         <v>230.3</v>
       </c>
       <c r="M64">
-        <v>44.6266576</v>
+        <v>45.3464424</v>
       </c>
       <c r="N64">
-        <v>185.6733424</v>
+        <v>184.9535576</v>
       </c>
       <c r="O64">
-        <v>54.773636008</v>
+        <v>54.561299492</v>
       </c>
       <c r="P64">
-        <v>130.899706392</v>
+        <v>130.392258108</v>
       </c>
       <c r="Q64">
-        <v>166.999706392</v>
+        <v>166.492258108</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1262258352306062</v>
+        <v>0.1281012950419223</v>
       </c>
       <c r="T64">
-        <v>1.244162092536808</v>
+        <v>1.273174859350173</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.160592623006568</v>
+        <v>5.078678454387417</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07195897416551125</v>
+        <v>0.07178050094339217</v>
       </c>
       <c r="C65">
-        <v>645.1270613354799</v>
+        <v>636.688330424861</v>
       </c>
       <c r="D65">
-        <v>1428.53506133548</v>
+        <v>1433.112330424861</v>
       </c>
       <c r="E65">
-        <v>248.4079999999999</v>
+        <v>261.424</v>
       </c>
       <c r="F65">
-        <v>820.0079999999999</v>
+        <v>833.024</v>
       </c>
       <c r="G65">
         <v>36.6</v>
@@ -6617,28 +6617,28 @@
         <v>230.3</v>
       </c>
       <c r="M65">
-        <v>45.3464424</v>
+        <v>46.0662272</v>
       </c>
       <c r="N65">
-        <v>184.9535576</v>
+        <v>184.2337728</v>
       </c>
       <c r="O65">
-        <v>54.561299492</v>
+        <v>54.348962976</v>
       </c>
       <c r="P65">
-        <v>130.392258108</v>
+        <v>129.884809824</v>
       </c>
       <c r="Q65">
-        <v>166.492258108</v>
+        <v>165.984809824</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1281012950419223</v>
+        <v>0.1300809470649782</v>
       </c>
       <c r="T65">
-        <v>1.273174859350173</v>
+        <v>1.30379944654206</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.078678454387417</v>
+        <v>4.999324103537613</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07178050094339217</v>
+        <v>0.07160202772127307</v>
       </c>
       <c r="C66">
-        <v>636.688330424861</v>
+        <v>628.2790264992709</v>
       </c>
       <c r="D66">
-        <v>1433.112330424861</v>
+        <v>1437.719026499271</v>
       </c>
       <c r="E66">
-        <v>261.424</v>
+        <v>274.4399999999999</v>
       </c>
       <c r="F66">
-        <v>833.024</v>
+        <v>846.04</v>
       </c>
       <c r="G66">
         <v>36.6</v>
@@ -6699,28 +6699,28 @@
         <v>230.3</v>
       </c>
       <c r="M66">
-        <v>46.0662272</v>
+        <v>46.786012</v>
       </c>
       <c r="N66">
-        <v>184.2337728</v>
+        <v>183.513988</v>
       </c>
       <c r="O66">
-        <v>54.348962976</v>
+        <v>54.13662646</v>
       </c>
       <c r="P66">
-        <v>129.884809824</v>
+        <v>129.37736154</v>
       </c>
       <c r="Q66">
-        <v>165.984809824</v>
+        <v>165.47736154</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1300809470649782</v>
+        <v>0.1321737220607802</v>
       </c>
       <c r="T66">
-        <v>1.30379944654206</v>
+        <v>1.336174010144911</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.999324103537613</v>
+        <v>4.92241142502165</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07160202772127307</v>
+        <v>0.07142355449915398</v>
       </c>
       <c r="C67">
-        <v>628.2790264992709</v>
+        <v>619.8994342502909</v>
       </c>
       <c r="D67">
-        <v>1437.719026499271</v>
+        <v>1442.355434250291</v>
       </c>
       <c r="E67">
-        <v>274.4399999999999</v>
+        <v>287.4559999999999</v>
       </c>
       <c r="F67">
-        <v>846.04</v>
+        <v>859.0559999999999</v>
       </c>
       <c r="G67">
         <v>36.6</v>
@@ -6781,28 +6781,28 @@
         <v>230.3</v>
       </c>
       <c r="M67">
-        <v>46.786012</v>
+        <v>47.5057968</v>
       </c>
       <c r="N67">
-        <v>183.513988</v>
+        <v>182.7942032</v>
       </c>
       <c r="O67">
-        <v>54.13662646</v>
+        <v>53.924289944</v>
       </c>
       <c r="P67">
-        <v>129.37736154</v>
+        <v>128.869913256</v>
       </c>
       <c r="Q67">
-        <v>165.47736154</v>
+        <v>164.969913256</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1321737220607802</v>
+        <v>0.1343896014680999</v>
       </c>
       <c r="T67">
-        <v>1.336174010144911</v>
+        <v>1.370452959842048</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.92241142502165</v>
+        <v>4.847829433733443</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07142355449915398</v>
+        <v>0.07124508127703488</v>
       </c>
       <c r="C68">
-        <v>619.8994342502909</v>
+        <v>611.5498420537191</v>
       </c>
       <c r="D68">
-        <v>1442.355434250291</v>
+        <v>1447.021842053719</v>
       </c>
       <c r="E68">
-        <v>287.4559999999999</v>
+        <v>300.472</v>
       </c>
       <c r="F68">
-        <v>859.0559999999999</v>
+        <v>872.072</v>
       </c>
       <c r="G68">
         <v>36.6</v>
@@ -6863,28 +6863,28 @@
         <v>230.3</v>
       </c>
       <c r="M68">
-        <v>47.5057968</v>
+        <v>48.22558160000001</v>
       </c>
       <c r="N68">
-        <v>182.7942032</v>
+        <v>182.0744184</v>
       </c>
       <c r="O68">
-        <v>53.924289944</v>
+        <v>53.711953428</v>
       </c>
       <c r="P68">
-        <v>128.869913256</v>
+        <v>128.362464972</v>
       </c>
       <c r="Q68">
-        <v>164.969913256</v>
+        <v>164.462464972</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1343896014680999</v>
+        <v>0.1367397765970754</v>
       </c>
       <c r="T68">
-        <v>1.370452959842048</v>
+        <v>1.406809421642041</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.847829433733443</v>
+        <v>4.775473770543391</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07124508127703488</v>
+        <v>0.0710666080549158</v>
       </c>
       <c r="C69">
-        <v>611.5498420537191</v>
+        <v>603.2305420293585</v>
       </c>
       <c r="D69">
-        <v>1447.021842053719</v>
+        <v>1451.718542029359</v>
       </c>
       <c r="E69">
-        <v>300.472</v>
+        <v>313.4879999999999</v>
       </c>
       <c r="F69">
-        <v>872.072</v>
+        <v>885.088</v>
       </c>
       <c r="G69">
         <v>36.6</v>
@@ -6945,28 +6945,28 @@
         <v>230.3</v>
       </c>
       <c r="M69">
-        <v>48.22558160000001</v>
+        <v>48.9453664</v>
       </c>
       <c r="N69">
-        <v>182.0744184</v>
+        <v>181.3546336</v>
       </c>
       <c r="O69">
-        <v>53.711953428</v>
+        <v>53.499616912</v>
       </c>
       <c r="P69">
-        <v>128.362464972</v>
+        <v>127.855016688</v>
       </c>
       <c r="Q69">
-        <v>164.462464972</v>
+        <v>163.955016688</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1367397765970754</v>
+        <v>0.1392368376716119</v>
       </c>
       <c r="T69">
-        <v>1.406809421642041</v>
+        <v>1.445438162304534</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.775473770543391</v>
+        <v>4.705246215094224</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0710666080549158</v>
+        <v>0.07088813483279671</v>
       </c>
       <c r="C70">
-        <v>603.2305420293585</v>
+        <v>594.9418301019778</v>
       </c>
       <c r="D70">
-        <v>1451.718542029359</v>
+        <v>1456.445830101978</v>
       </c>
       <c r="E70">
-        <v>313.4879999999999</v>
+        <v>326.504</v>
       </c>
       <c r="F70">
-        <v>885.088</v>
+        <v>898.104</v>
       </c>
       <c r="G70">
         <v>36.6</v>
@@ -7027,28 +7027,28 @@
         <v>230.3</v>
       </c>
       <c r="M70">
-        <v>48.9453664</v>
+        <v>49.6651512</v>
       </c>
       <c r="N70">
-        <v>181.3546336</v>
+        <v>180.6348488</v>
       </c>
       <c r="O70">
-        <v>53.499616912</v>
+        <v>53.287280396</v>
       </c>
       <c r="P70">
-        <v>127.855016688</v>
+        <v>127.347568404</v>
       </c>
       <c r="Q70">
-        <v>163.955016688</v>
+        <v>163.447568404</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1392368376716119</v>
+        <v>0.1418949994606345</v>
       </c>
       <c r="T70">
-        <v>1.445438162304534</v>
+        <v>1.486559079783962</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.705246215094224</v>
+        <v>4.637054240962423</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07088813483279671</v>
+        <v>0.07070966161067761</v>
       </c>
       <c r="C71">
-        <v>594.9418301019778</v>
+        <v>586.6840060634639</v>
       </c>
       <c r="D71">
-        <v>1456.445830101978</v>
+        <v>1461.204006063464</v>
       </c>
       <c r="E71">
-        <v>326.504</v>
+        <v>339.52</v>
       </c>
       <c r="F71">
-        <v>898.104</v>
+        <v>911.12</v>
       </c>
       <c r="G71">
         <v>36.6</v>
@@ -7109,28 +7109,28 @@
         <v>230.3</v>
       </c>
       <c r="M71">
-        <v>49.6651512</v>
+        <v>50.384936</v>
       </c>
       <c r="N71">
-        <v>180.6348488</v>
+        <v>179.915064</v>
       </c>
       <c r="O71">
-        <v>53.287280396</v>
+        <v>53.07494388</v>
       </c>
       <c r="P71">
-        <v>127.347568404</v>
+        <v>126.84012012</v>
       </c>
       <c r="Q71">
-        <v>163.447568404</v>
+        <v>162.94012012</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1418949994606345</v>
+        <v>0.1447303720355921</v>
       </c>
       <c r="T71">
-        <v>1.486559079783962</v>
+        <v>1.530421391762019</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.637054240962423</v>
+        <v>4.570810608948674</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07070966161067761</v>
+        <v>0.07053118838855853</v>
       </c>
       <c r="C72">
-        <v>586.6840060634639</v>
+        <v>578.4573736361973</v>
       </c>
       <c r="D72">
-        <v>1461.204006063464</v>
+        <v>1465.993373636197</v>
       </c>
       <c r="E72">
-        <v>339.52</v>
+        <v>352.5360000000001</v>
       </c>
       <c r="F72">
-        <v>911.12</v>
+        <v>924.1360000000001</v>
       </c>
       <c r="G72">
         <v>36.6</v>
@@ -7191,28 +7191,28 @@
         <v>230.3</v>
       </c>
       <c r="M72">
-        <v>50.384936</v>
+        <v>51.10472080000001</v>
       </c>
       <c r="N72">
-        <v>179.915064</v>
+        <v>179.1952792</v>
       </c>
       <c r="O72">
-        <v>53.07494388</v>
+        <v>52.862607364</v>
       </c>
       <c r="P72">
-        <v>126.84012012</v>
+        <v>126.332671836</v>
       </c>
       <c r="Q72">
-        <v>162.94012012</v>
+        <v>162.432671836</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1447303720355921</v>
+        <v>0.1477612875467536</v>
       </c>
       <c r="T72">
-        <v>1.530421391762019</v>
+        <v>1.577308690773045</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.570810608948674</v>
+        <v>4.506432994738129</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07053118838855853</v>
+        <v>0.07162171516643943</v>
       </c>
       <c r="C73">
-        <v>578.4573736361975</v>
+        <v>536.6574074228052</v>
       </c>
       <c r="D73">
-        <v>1465.993373636197</v>
+        <v>1437.209407422805</v>
       </c>
       <c r="E73">
-        <v>352.5359999999998</v>
+        <v>365.5519999999999</v>
       </c>
       <c r="F73">
-        <v>924.1359999999999</v>
+        <v>937.1519999999999</v>
       </c>
       <c r="G73">
         <v>36.6</v>
@@ -7273,45 +7273,45 @@
         <v>230.3</v>
       </c>
       <c r="M73">
-        <v>51.1047208</v>
+        <v>54.1673856</v>
       </c>
       <c r="N73">
-        <v>179.1952792</v>
+        <v>176.1326144</v>
       </c>
       <c r="O73">
-        <v>52.862607364</v>
+        <v>51.959121248</v>
       </c>
       <c r="P73">
-        <v>126.332671836</v>
+        <v>124.173493152</v>
       </c>
       <c r="Q73">
-        <v>162.432671836</v>
+        <v>160.273493152</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1477612875467535</v>
+        <v>0.151008697022998</v>
       </c>
       <c r="T73">
-        <v>1.577308690773044</v>
+        <v>1.627545082570572</v>
       </c>
       <c r="U73">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V73">
         <v>0.295</v>
       </c>
       <c r="W73">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.50643299473813</v>
+        <v>4.251635877364553</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07162171516643943</v>
+        <v>0.07146086694432034</v>
       </c>
       <c r="C74">
-        <v>536.6574074228052</v>
+        <v>527.8156545075879</v>
       </c>
       <c r="D74">
-        <v>1437.209407422805</v>
+        <v>1441.383654507588</v>
       </c>
       <c r="E74">
-        <v>365.5519999999999</v>
+        <v>378.5679999999999</v>
       </c>
       <c r="F74">
-        <v>937.1519999999999</v>
+        <v>950.1679999999999</v>
       </c>
       <c r="G74">
         <v>36.6</v>
@@ -7355,28 +7355,28 @@
         <v>230.3</v>
       </c>
       <c r="M74">
-        <v>54.1673856</v>
+        <v>54.9197104</v>
       </c>
       <c r="N74">
-        <v>176.1326144</v>
+        <v>175.3802896</v>
       </c>
       <c r="O74">
-        <v>51.959121248</v>
+        <v>51.737185432</v>
       </c>
       <c r="P74">
-        <v>124.173493152</v>
+        <v>123.643104168</v>
       </c>
       <c r="Q74">
-        <v>160.273493152</v>
+        <v>159.743104168</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.151008697022998</v>
+        <v>0.1544966553493346</v>
       </c>
       <c r="T74">
-        <v>1.627545082570572</v>
+        <v>1.681502688575324</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.251635877364553</v>
+        <v>4.193394290003394</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07146086694432034</v>
+        <v>0.07130001872220125</v>
       </c>
       <c r="C75">
-        <v>527.8156545075879</v>
+        <v>518.9982196819849</v>
       </c>
       <c r="D75">
-        <v>1441.383654507588</v>
+        <v>1445.582219681985</v>
       </c>
       <c r="E75">
-        <v>378.5679999999999</v>
+        <v>391.5839999999999</v>
       </c>
       <c r="F75">
-        <v>950.1679999999999</v>
+        <v>963.184</v>
       </c>
       <c r="G75">
         <v>36.6</v>
@@ -7437,28 +7437,28 @@
         <v>230.3</v>
       </c>
       <c r="M75">
-        <v>54.9197104</v>
+        <v>55.6720352</v>
       </c>
       <c r="N75">
-        <v>175.3802896</v>
+        <v>174.6279648</v>
       </c>
       <c r="O75">
-        <v>51.737185432</v>
+        <v>51.515249616</v>
       </c>
       <c r="P75">
-        <v>123.643104168</v>
+        <v>123.112715184</v>
       </c>
       <c r="Q75">
-        <v>159.743104168</v>
+        <v>159.212715184</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1544966553493346</v>
+        <v>0.1582529181623125</v>
       </c>
       <c r="T75">
-        <v>1.681502688575324</v>
+        <v>1.739610879657365</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.193394290003394</v>
+        <v>4.136726799597943</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07130001872220125</v>
+        <v>0.07113917050008216</v>
       </c>
       <c r="C76">
-        <v>518.9982196819849</v>
+        <v>510.2053160732092</v>
       </c>
       <c r="D76">
-        <v>1445.582219681985</v>
+        <v>1449.805316073209</v>
       </c>
       <c r="E76">
-        <v>391.5839999999999</v>
+        <v>404.5999999999999</v>
       </c>
       <c r="F76">
-        <v>963.184</v>
+        <v>976.1999999999999</v>
       </c>
       <c r="G76">
         <v>36.6</v>
@@ -7519,28 +7519,28 @@
         <v>230.3</v>
       </c>
       <c r="M76">
-        <v>55.6720352</v>
+        <v>56.42436</v>
       </c>
       <c r="N76">
-        <v>174.6279648</v>
+        <v>173.87564</v>
       </c>
       <c r="O76">
-        <v>51.515249616</v>
+        <v>51.2933138</v>
       </c>
       <c r="P76">
-        <v>123.112715184</v>
+        <v>122.5823262</v>
       </c>
       <c r="Q76">
-        <v>159.212715184</v>
+        <v>158.6823262</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1582529181623125</v>
+        <v>0.1623096820003286</v>
       </c>
       <c r="T76">
-        <v>1.739610879657365</v>
+        <v>1.802367726025969</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.136726799597943</v>
+        <v>4.08157044226997</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07113917050008216</v>
+        <v>0.07097832227796307</v>
       </c>
       <c r="C77">
-        <v>510.2053160732092</v>
+        <v>501.4371593062738</v>
       </c>
       <c r="D77">
-        <v>1449.805316073209</v>
+        <v>1454.053159306274</v>
       </c>
       <c r="E77">
-        <v>404.5999999999999</v>
+        <v>417.6159999999999</v>
       </c>
       <c r="F77">
-        <v>976.1999999999999</v>
+        <v>989.2159999999999</v>
       </c>
       <c r="G77">
         <v>36.6</v>
@@ -7601,28 +7601,28 @@
         <v>230.3</v>
       </c>
       <c r="M77">
-        <v>56.42436</v>
+        <v>57.1766848</v>
       </c>
       <c r="N77">
-        <v>173.87564</v>
+        <v>173.1233152</v>
       </c>
       <c r="O77">
-        <v>51.2933138</v>
+        <v>51.071377984</v>
       </c>
       <c r="P77">
-        <v>122.5823262</v>
+        <v>122.051937216</v>
       </c>
       <c r="Q77">
-        <v>158.6823262</v>
+        <v>158.151937216</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1623096820003286</v>
+        <v>0.1667045094915127</v>
       </c>
       <c r="T77">
-        <v>1.802367726025969</v>
+        <v>1.870354309591956</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.08157044226997</v>
+        <v>4.027865568029576</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07097832227796307</v>
+        <v>0.07271744905584397</v>
       </c>
       <c r="C78">
-        <v>501.4371593062738</v>
+        <v>443.7724002280315</v>
       </c>
       <c r="D78">
-        <v>1454.053159306274</v>
+        <v>1409.404400228032</v>
       </c>
       <c r="E78">
-        <v>417.6159999999999</v>
+        <v>430.6319999999999</v>
       </c>
       <c r="F78">
-        <v>989.2159999999999</v>
+        <v>1002.232</v>
       </c>
       <c r="G78">
         <v>36.6</v>
@@ -7683,45 +7683,45 @@
         <v>230.3</v>
       </c>
       <c r="M78">
-        <v>57.1766848</v>
+        <v>61.4368216</v>
       </c>
       <c r="N78">
-        <v>173.1233152</v>
+        <v>168.8631784</v>
       </c>
       <c r="O78">
-        <v>51.071377984</v>
+        <v>49.814637628</v>
       </c>
       <c r="P78">
-        <v>122.051937216</v>
+        <v>119.048540772</v>
       </c>
       <c r="Q78">
-        <v>158.151937216</v>
+        <v>155.148540772</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1667045094915127</v>
+        <v>0.1714814958949738</v>
       </c>
       <c r="T78">
-        <v>1.870354309591956</v>
+        <v>1.944252769989769</v>
       </c>
       <c r="U78">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V78">
         <v>0.295</v>
       </c>
       <c r="W78">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>4.027865568029576</v>
+        <v>3.748566315806936</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07271744905584397</v>
+        <v>0.07258127583372488</v>
       </c>
       <c r="C79">
-        <v>443.7724002280315</v>
+        <v>434.1532053930003</v>
       </c>
       <c r="D79">
-        <v>1409.404400228032</v>
+        <v>1412.801205393</v>
       </c>
       <c r="E79">
-        <v>430.6319999999999</v>
+        <v>443.6479999999999</v>
       </c>
       <c r="F79">
-        <v>1002.232</v>
+        <v>1015.248</v>
       </c>
       <c r="G79">
         <v>36.6</v>
@@ -7765,28 +7765,28 @@
         <v>230.3</v>
       </c>
       <c r="M79">
-        <v>61.4368216</v>
+        <v>62.2347024</v>
       </c>
       <c r="N79">
-        <v>168.8631784</v>
+        <v>168.0652976</v>
       </c>
       <c r="O79">
-        <v>49.814637628</v>
+        <v>49.579262792</v>
       </c>
       <c r="P79">
-        <v>119.048540772</v>
+        <v>118.486034808</v>
       </c>
       <c r="Q79">
-        <v>155.148540772</v>
+        <v>154.586034808</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1714814958949738</v>
+        <v>0.1766927537896586</v>
       </c>
       <c r="T79">
-        <v>1.944252769989769</v>
+        <v>2.024869272241928</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.748566315806936</v>
+        <v>3.700507773296591</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07258127583372488</v>
+        <v>0.07244510261160579</v>
       </c>
       <c r="C80">
-        <v>434.1532053930003</v>
+        <v>424.5504233929628</v>
       </c>
       <c r="D80">
-        <v>1412.801205393</v>
+        <v>1416.214423392963</v>
       </c>
       <c r="E80">
-        <v>443.6479999999999</v>
+        <v>456.6639999999999</v>
       </c>
       <c r="F80">
-        <v>1015.248</v>
+        <v>1028.264</v>
       </c>
       <c r="G80">
         <v>36.6</v>
@@ -7847,28 +7847,28 @@
         <v>230.3</v>
       </c>
       <c r="M80">
-        <v>62.2347024</v>
+        <v>63.03258319999999</v>
       </c>
       <c r="N80">
-        <v>168.0652976</v>
+        <v>167.2674168</v>
       </c>
       <c r="O80">
-        <v>49.579262792</v>
+        <v>49.34388795600001</v>
       </c>
       <c r="P80">
-        <v>118.486034808</v>
+        <v>117.923528844</v>
       </c>
       <c r="Q80">
-        <v>154.586034808</v>
+        <v>154.023528844</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1766927537896586</v>
+        <v>0.1824003219600276</v>
       </c>
       <c r="T80">
-        <v>2.024869272241928</v>
+        <v>2.113163536613341</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.700507773296591</v>
+        <v>3.653665902748534</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07244510261160579</v>
+        <v>0.0723089293894867</v>
       </c>
       <c r="C81">
-        <v>424.5504233929628</v>
+        <v>414.9641734724084</v>
       </c>
       <c r="D81">
-        <v>1416.214423392963</v>
+        <v>1419.644173472409</v>
       </c>
       <c r="E81">
-        <v>456.6639999999999</v>
+        <v>469.6799999999999</v>
       </c>
       <c r="F81">
-        <v>1028.264</v>
+        <v>1041.28</v>
       </c>
       <c r="G81">
         <v>36.6</v>
@@ -7929,28 +7929,28 @@
         <v>230.3</v>
       </c>
       <c r="M81">
-        <v>63.03258319999999</v>
+        <v>63.830464</v>
       </c>
       <c r="N81">
-        <v>167.2674168</v>
+        <v>166.469536</v>
       </c>
       <c r="O81">
-        <v>49.34388795600001</v>
+        <v>49.10851312</v>
       </c>
       <c r="P81">
-        <v>117.923528844</v>
+        <v>117.36102288</v>
       </c>
       <c r="Q81">
-        <v>154.023528844</v>
+        <v>153.46102288</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1824003219600276</v>
+        <v>0.1886786469474335</v>
       </c>
       <c r="T81">
-        <v>2.113163536613341</v>
+        <v>2.210287227421895</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.653665902748534</v>
+        <v>3.607995078964176</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0723089293894867</v>
+        <v>0.0721727561673676</v>
       </c>
       <c r="C82">
-        <v>414.9641734724084</v>
+        <v>405.3945760337642</v>
       </c>
       <c r="D82">
-        <v>1419.644173472409</v>
+        <v>1423.090576033764</v>
       </c>
       <c r="E82">
-        <v>469.6799999999999</v>
+        <v>482.696</v>
       </c>
       <c r="F82">
-        <v>1041.28</v>
+        <v>1054.296</v>
       </c>
       <c r="G82">
         <v>36.6</v>
@@ -8011,28 +8011,28 @@
         <v>230.3</v>
       </c>
       <c r="M82">
-        <v>63.830464</v>
+        <v>64.62834480000001</v>
       </c>
       <c r="N82">
-        <v>166.469536</v>
+        <v>165.6716552</v>
       </c>
       <c r="O82">
-        <v>49.10851312</v>
+        <v>48.873138284</v>
       </c>
       <c r="P82">
-        <v>117.36102288</v>
+        <v>116.798516916</v>
       </c>
       <c r="Q82">
-        <v>153.46102288</v>
+        <v>152.898516916</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1886786469474335</v>
+        <v>0.1956178482493032</v>
       </c>
       <c r="T82">
-        <v>2.210287227421895</v>
+        <v>2.317634464631348</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.607995078964176</v>
+        <v>3.563451929841162</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0721727561673676</v>
+        <v>0.07203658294524851</v>
       </c>
       <c r="C83">
-        <v>405.3945760337642</v>
+        <v>395.8417526514825</v>
       </c>
       <c r="D83">
-        <v>1423.090576033764</v>
+        <v>1426.553752651482</v>
       </c>
       <c r="E83">
-        <v>482.696</v>
+        <v>495.7119999999999</v>
       </c>
       <c r="F83">
-        <v>1054.296</v>
+        <v>1067.312</v>
       </c>
       <c r="G83">
         <v>36.6</v>
@@ -8093,28 +8093,28 @@
         <v>230.3</v>
       </c>
       <c r="M83">
-        <v>64.62834480000001</v>
+        <v>65.4262256</v>
       </c>
       <c r="N83">
-        <v>165.6716552</v>
+        <v>164.8737744</v>
       </c>
       <c r="O83">
-        <v>48.873138284</v>
+        <v>48.637763448</v>
       </c>
       <c r="P83">
-        <v>116.798516916</v>
+        <v>116.236010952</v>
       </c>
       <c r="Q83">
-        <v>152.898516916</v>
+        <v>152.336010952</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1956178482493032</v>
+        <v>0.2033280719180473</v>
       </c>
       <c r="T83">
-        <v>2.317634464631348</v>
+        <v>2.436909172641853</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.563451929841162</v>
+        <v>3.51999519898944</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07203658294524851</v>
+        <v>0.07353882972312942</v>
       </c>
       <c r="C84">
-        <v>395.8417526514825</v>
+        <v>345.5287291401248</v>
       </c>
       <c r="D84">
-        <v>1426.553752651482</v>
+        <v>1389.256729140125</v>
       </c>
       <c r="E84">
-        <v>495.7119999999999</v>
+        <v>508.728</v>
       </c>
       <c r="F84">
-        <v>1067.312</v>
+        <v>1080.328</v>
       </c>
       <c r="G84">
         <v>36.6</v>
@@ -8175,45 +8175,45 @@
         <v>230.3</v>
       </c>
       <c r="M84">
-        <v>65.4262256</v>
+        <v>69.2490248</v>
       </c>
       <c r="N84">
-        <v>164.8737744</v>
+        <v>161.0509752</v>
       </c>
       <c r="O84">
-        <v>48.637763448</v>
+        <v>47.510037684</v>
       </c>
       <c r="P84">
-        <v>116.236010952</v>
+        <v>113.540937516</v>
       </c>
       <c r="Q84">
-        <v>152.336010952</v>
+        <v>149.640937516</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2033280719180473</v>
+        <v>0.2119453807242908</v>
       </c>
       <c r="T84">
-        <v>2.436909172641853</v>
+        <v>2.57021619924183</v>
       </c>
       <c r="U84">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V84">
         <v>0.295</v>
       </c>
       <c r="W84">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y84">
-        <v>3.51999519898944</v>
+        <v>3.325678602191666</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07353882972312942</v>
+        <v>0.07342239650101035</v>
       </c>
       <c r="C85">
-        <v>345.5287291401248</v>
+        <v>335.3336124276091</v>
       </c>
       <c r="D85">
-        <v>1389.256729140125</v>
+        <v>1392.077612427609</v>
       </c>
       <c r="E85">
-        <v>508.728</v>
+        <v>521.744</v>
       </c>
       <c r="F85">
-        <v>1080.328</v>
+        <v>1093.344</v>
       </c>
       <c r="G85">
         <v>36.6</v>
@@ -8257,28 +8257,28 @@
         <v>230.3</v>
       </c>
       <c r="M85">
-        <v>69.2490248</v>
+        <v>70.08335040000001</v>
       </c>
       <c r="N85">
-        <v>161.0509752</v>
+        <v>160.2166496</v>
       </c>
       <c r="O85">
-        <v>47.510037684</v>
+        <v>47.263911632</v>
       </c>
       <c r="P85">
-        <v>113.540937516</v>
+        <v>112.952737968</v>
       </c>
       <c r="Q85">
-        <v>149.640937516</v>
+        <v>149.0527379679999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2119453807242908</v>
+        <v>0.2216398531313147</v>
       </c>
       <c r="T85">
-        <v>2.57021619924183</v>
+        <v>2.720186604166803</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.325678602191666</v>
+        <v>3.286087190260812</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07342239650101035</v>
+        <v>0.07330596327889125</v>
       </c>
       <c r="C86">
-        <v>335.3336124276093</v>
+        <v>325.1499746198635</v>
       </c>
       <c r="D86">
-        <v>1392.077612427609</v>
+        <v>1394.909974619864</v>
       </c>
       <c r="E86">
-        <v>521.7439999999998</v>
+        <v>534.7599999999999</v>
       </c>
       <c r="F86">
-        <v>1093.344</v>
+        <v>1106.36</v>
       </c>
       <c r="G86">
         <v>36.6</v>
@@ -8339,28 +8339,28 @@
         <v>230.3</v>
       </c>
       <c r="M86">
-        <v>70.08335039999999</v>
+        <v>70.917676</v>
       </c>
       <c r="N86">
-        <v>160.2166496</v>
+        <v>159.382324</v>
       </c>
       <c r="O86">
-        <v>47.26391163200001</v>
+        <v>47.01778558</v>
       </c>
       <c r="P86">
-        <v>112.952737968</v>
+        <v>112.36453842</v>
       </c>
       <c r="Q86">
-        <v>149.052737968</v>
+        <v>148.46453842</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2216398531313146</v>
+        <v>0.2326269218592749</v>
       </c>
       <c r="T86">
-        <v>2.720186604166801</v>
+        <v>2.89015306308177</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.286087190260814</v>
+        <v>3.247427340963627</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07330596327889125</v>
+        <v>0.07318953005677216</v>
       </c>
       <c r="C87">
-        <v>325.1499746198635</v>
+        <v>314.9778859256905</v>
       </c>
       <c r="D87">
-        <v>1394.909974619864</v>
+        <v>1397.753885925691</v>
       </c>
       <c r="E87">
-        <v>534.7599999999999</v>
+        <v>547.776</v>
       </c>
       <c r="F87">
-        <v>1106.36</v>
+        <v>1119.376</v>
       </c>
       <c r="G87">
         <v>36.6</v>
@@ -8421,28 +8421,28 @@
         <v>230.3</v>
       </c>
       <c r="M87">
-        <v>70.917676</v>
+        <v>71.7520016</v>
       </c>
       <c r="N87">
-        <v>159.382324</v>
+        <v>158.5479984</v>
       </c>
       <c r="O87">
-        <v>47.01778558</v>
+        <v>46.771659528</v>
       </c>
       <c r="P87">
-        <v>112.36453842</v>
+        <v>111.776338872</v>
       </c>
       <c r="Q87">
-        <v>148.46453842</v>
+        <v>147.876338872</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2326269218592749</v>
+        <v>0.2451835718340868</v>
       </c>
       <c r="T87">
-        <v>2.89015306308177</v>
+        <v>3.084400444698877</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.247427340963627</v>
+        <v>3.209666557929166</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07318953005677216</v>
+        <v>0.07307309683465307</v>
       </c>
       <c r="C88">
-        <v>314.9778859256905</v>
+        <v>304.8174171276257</v>
       </c>
       <c r="D88">
-        <v>1397.753885925691</v>
+        <v>1400.609417127626</v>
       </c>
       <c r="E88">
-        <v>547.776</v>
+        <v>560.7919999999998</v>
       </c>
       <c r="F88">
-        <v>1119.376</v>
+        <v>1132.392</v>
       </c>
       <c r="G88">
         <v>36.6</v>
@@ -8503,28 +8503,28 @@
         <v>230.3</v>
       </c>
       <c r="M88">
-        <v>71.7520016</v>
+        <v>72.5863272</v>
       </c>
       <c r="N88">
-        <v>158.5479984</v>
+        <v>157.7136728</v>
       </c>
       <c r="O88">
-        <v>46.771659528</v>
+        <v>46.525533476</v>
       </c>
       <c r="P88">
-        <v>111.776338872</v>
+        <v>111.188139324</v>
       </c>
       <c r="Q88">
-        <v>147.876338872</v>
+        <v>147.288139324</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2451835718340868</v>
+        <v>0.2596720141127158</v>
       </c>
       <c r="T88">
-        <v>3.084400444698877</v>
+        <v>3.308532038872463</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.209666557929166</v>
+        <v>3.172773838872509</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07307309683465307</v>
+        <v>0.07295666361253397</v>
       </c>
       <c r="C89">
-        <v>304.8174171276257</v>
+        <v>294.6686395878057</v>
       </c>
       <c r="D89">
-        <v>1400.609417127626</v>
+        <v>1403.476639587806</v>
       </c>
       <c r="E89">
-        <v>560.7919999999998</v>
+        <v>573.8079999999999</v>
       </c>
       <c r="F89">
-        <v>1132.392</v>
+        <v>1145.408</v>
       </c>
       <c r="G89">
         <v>36.6</v>
@@ -8585,28 +8585,28 @@
         <v>230.3</v>
       </c>
       <c r="M89">
-        <v>72.5863272</v>
+        <v>73.4206528</v>
       </c>
       <c r="N89">
-        <v>157.7136728</v>
+        <v>156.8793472</v>
       </c>
       <c r="O89">
-        <v>46.525533476</v>
+        <v>46.279407424</v>
       </c>
       <c r="P89">
-        <v>111.188139324</v>
+        <v>110.599939776</v>
       </c>
       <c r="Q89">
-        <v>147.288139324</v>
+        <v>146.699939776</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2596720141127158</v>
+        <v>0.2765751967711164</v>
       </c>
       <c r="T89">
-        <v>3.308532038872463</v>
+        <v>3.570018898741646</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.172773838872509</v>
+        <v>3.136719590703503</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07295666361253397</v>
+        <v>0.07284023039041487</v>
       </c>
       <c r="C90">
-        <v>294.6686395878057</v>
+        <v>284.5316252539155</v>
       </c>
       <c r="D90">
-        <v>1403.476639587806</v>
+        <v>1406.355625253916</v>
       </c>
       <c r="E90">
-        <v>573.8079999999999</v>
+        <v>586.824</v>
       </c>
       <c r="F90">
-        <v>1145.408</v>
+        <v>1158.424</v>
       </c>
       <c r="G90">
         <v>36.6</v>
@@ -8667,28 +8667,28 @@
         <v>230.3</v>
       </c>
       <c r="M90">
-        <v>73.4206528</v>
+        <v>74.2549784</v>
       </c>
       <c r="N90">
-        <v>156.8793472</v>
+        <v>156.0450216</v>
       </c>
       <c r="O90">
-        <v>46.279407424</v>
+        <v>46.033281372</v>
       </c>
       <c r="P90">
-        <v>110.599939776</v>
+        <v>110.011740228</v>
       </c>
       <c r="Q90">
-        <v>146.699939776</v>
+        <v>146.111740228</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2765751967711164</v>
+        <v>0.2965516853674079</v>
       </c>
       <c r="T90">
-        <v>3.570018898741646</v>
+        <v>3.87904882404159</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.136719590703503</v>
+        <v>3.10147555035852</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07284023039041487</v>
+        <v>0.0727237971682958</v>
       </c>
       <c r="C91">
-        <v>284.5316252539155</v>
+        <v>274.4064466652044</v>
       </c>
       <c r="D91">
-        <v>1406.355625253916</v>
+        <v>1409.246446665205</v>
       </c>
       <c r="E91">
-        <v>586.824</v>
+        <v>599.84</v>
       </c>
       <c r="F91">
-        <v>1158.424</v>
+        <v>1171.44</v>
       </c>
       <c r="G91">
         <v>36.6</v>
@@ -8749,28 +8749,28 @@
         <v>230.3</v>
       </c>
       <c r="M91">
-        <v>74.2549784</v>
+        <v>75.08930400000001</v>
       </c>
       <c r="N91">
-        <v>156.0450216</v>
+        <v>155.210696</v>
       </c>
       <c r="O91">
-        <v>46.033281372</v>
+        <v>45.78715532</v>
       </c>
       <c r="P91">
-        <v>110.011740228</v>
+        <v>109.42354068</v>
       </c>
       <c r="Q91">
-        <v>146.111740228</v>
+        <v>145.5235406799999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2965516853674079</v>
+        <v>0.3205234716829579</v>
       </c>
       <c r="T91">
-        <v>3.87904882404159</v>
+        <v>4.249884734401522</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.10147555035852</v>
+        <v>3.067014710910091</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0727237971682958</v>
+        <v>0.0726073639461767</v>
       </c>
       <c r="C92">
-        <v>274.4064466652044</v>
+        <v>264.2931769585823</v>
       </c>
       <c r="D92">
-        <v>1409.246446665205</v>
+        <v>1412.149176958582</v>
       </c>
       <c r="E92">
-        <v>599.84</v>
+        <v>612.8559999999999</v>
       </c>
       <c r="F92">
-        <v>1171.44</v>
+        <v>1184.456</v>
       </c>
       <c r="G92">
         <v>36.6</v>
@@ -8831,28 +8831,28 @@
         <v>230.3</v>
       </c>
       <c r="M92">
-        <v>75.08930400000001</v>
+        <v>75.9236296</v>
       </c>
       <c r="N92">
-        <v>155.210696</v>
+        <v>154.3763704</v>
       </c>
       <c r="O92">
-        <v>45.78715532</v>
+        <v>45.541029268</v>
       </c>
       <c r="P92">
-        <v>109.42354068</v>
+        <v>108.835341132</v>
       </c>
       <c r="Q92">
-        <v>145.5235406799999</v>
+        <v>144.935341132</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3205234716829579</v>
+        <v>0.3498223216241856</v>
       </c>
       <c r="T92">
-        <v>4.249884734401522</v>
+        <v>4.703128624841441</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.067014710910091</v>
+        <v>3.033311252548442</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0726073639461767</v>
+        <v>0.0724909307240576</v>
       </c>
       <c r="C93">
-        <v>264.2931769585823</v>
+        <v>254.1918898747829</v>
       </c>
       <c r="D93">
-        <v>1412.149176958582</v>
+        <v>1415.063889874783</v>
       </c>
       <c r="E93">
-        <v>612.8559999999999</v>
+        <v>625.872</v>
       </c>
       <c r="F93">
-        <v>1184.456</v>
+        <v>1197.472</v>
       </c>
       <c r="G93">
         <v>36.6</v>
@@ -8913,28 +8913,28 @@
         <v>230.3</v>
       </c>
       <c r="M93">
-        <v>75.9236296</v>
+        <v>76.7579552</v>
       </c>
       <c r="N93">
-        <v>154.3763704</v>
+        <v>153.5420448</v>
       </c>
       <c r="O93">
-        <v>45.541029268</v>
+        <v>45.294903216</v>
       </c>
       <c r="P93">
-        <v>108.835341132</v>
+        <v>108.247141584</v>
       </c>
       <c r="Q93">
-        <v>144.935341132</v>
+        <v>144.347141584</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3498223216241856</v>
+        <v>0.3864458840507202</v>
       </c>
       <c r="T93">
-        <v>4.703128624841441</v>
+        <v>5.269683487891339</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.033311252548442</v>
+        <v>3.000340478064221</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0724909307240576</v>
+        <v>0.07748856750193853</v>
       </c>
       <c r="C94">
-        <v>254.1918898747829</v>
+        <v>126.0128283863121</v>
       </c>
       <c r="D94">
-        <v>1415.063889874783</v>
+        <v>1299.900828386312</v>
       </c>
       <c r="E94">
-        <v>625.872</v>
+        <v>638.888</v>
       </c>
       <c r="F94">
-        <v>1197.472</v>
+        <v>1210.488</v>
       </c>
       <c r="G94">
         <v>36.6</v>
@@ -8995,45 +8995,45 @@
         <v>230.3</v>
       </c>
       <c r="M94">
-        <v>76.7579552</v>
+        <v>87.03408720000002</v>
       </c>
       <c r="N94">
-        <v>153.5420448</v>
+        <v>143.2659128</v>
       </c>
       <c r="O94">
-        <v>45.294903216</v>
+        <v>42.26344427599999</v>
       </c>
       <c r="P94">
-        <v>108.247141584</v>
+        <v>101.002468524</v>
       </c>
       <c r="Q94">
-        <v>144.347141584</v>
+        <v>137.102468524</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3864458840507202</v>
+        <v>0.4335333214562647</v>
       </c>
       <c r="T94">
-        <v>5.269683487891339</v>
+        <v>5.998111168955493</v>
       </c>
       <c r="U94">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V94">
         <v>0.295</v>
       </c>
       <c r="W94">
-        <v>0.04519050000000001</v>
+        <v>0.05068950000000001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y94">
-        <v>3.000340478064221</v>
+        <v>2.646089680595857</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07748856750193853</v>
+        <v>0.07742712427981943</v>
       </c>
       <c r="C95">
-        <v>126.0128283863121</v>
+        <v>114.2987697508916</v>
       </c>
       <c r="D95">
-        <v>1299.900828386312</v>
+        <v>1301.202769750892</v>
       </c>
       <c r="E95">
-        <v>638.888</v>
+        <v>651.9039999999999</v>
       </c>
       <c r="F95">
-        <v>1210.488</v>
+        <v>1223.504</v>
       </c>
       <c r="G95">
         <v>36.6</v>
@@ -9077,28 +9077,28 @@
         <v>230.3</v>
       </c>
       <c r="M95">
-        <v>87.03408720000002</v>
+        <v>87.96993759999999</v>
       </c>
       <c r="N95">
-        <v>143.2659128</v>
+        <v>142.3300624</v>
       </c>
       <c r="O95">
-        <v>42.26344427599999</v>
+        <v>41.98736840800001</v>
       </c>
       <c r="P95">
-        <v>101.002468524</v>
+        <v>100.342693992</v>
       </c>
       <c r="Q95">
-        <v>137.102468524</v>
+        <v>136.442693992</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4335333214562647</v>
+        <v>0.4963165713303241</v>
       </c>
       <c r="T95">
-        <v>5.998111168955493</v>
+        <v>6.969348077041032</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.646089680595857</v>
+        <v>2.617939790376753</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07742712427981943</v>
+        <v>0.07736568105770034</v>
       </c>
       <c r="C96">
-        <v>114.2987697508916</v>
+        <v>102.5873217003614</v>
       </c>
       <c r="D96">
-        <v>1301.202769750892</v>
+        <v>1302.507321700361</v>
       </c>
       <c r="E96">
-        <v>651.9039999999999</v>
+        <v>664.92</v>
       </c>
       <c r="F96">
-        <v>1223.504</v>
+        <v>1236.52</v>
       </c>
       <c r="G96">
         <v>36.6</v>
@@ -9159,28 +9159,28 @@
         <v>230.3</v>
       </c>
       <c r="M96">
-        <v>87.96993759999999</v>
+        <v>88.905788</v>
       </c>
       <c r="N96">
-        <v>142.3300624</v>
+        <v>141.394212</v>
       </c>
       <c r="O96">
-        <v>41.98736840800001</v>
+        <v>41.71129254</v>
       </c>
       <c r="P96">
-        <v>100.342693992</v>
+        <v>99.68291946000001</v>
       </c>
       <c r="Q96">
-        <v>136.442693992</v>
+        <v>135.78291946</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4963165713303241</v>
+        <v>0.5842131211540073</v>
       </c>
       <c r="T96">
-        <v>6.969348077041032</v>
+        <v>8.329079748360789</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.617939790376753</v>
+        <v>2.590382529425418</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07736568105770034</v>
+        <v>0.07730423783558124</v>
       </c>
       <c r="C97">
-        <v>102.5873217003614</v>
+        <v>90.8784920945152</v>
       </c>
       <c r="D97">
-        <v>1302.507321700361</v>
+        <v>1303.814492094515</v>
       </c>
       <c r="E97">
-        <v>664.92</v>
+        <v>677.936</v>
       </c>
       <c r="F97">
-        <v>1236.52</v>
+        <v>1249.536</v>
       </c>
       <c r="G97">
         <v>36.6</v>
@@ -9241,28 +9241,28 @@
         <v>230.3</v>
       </c>
       <c r="M97">
-        <v>88.905788</v>
+        <v>89.84163840000001</v>
       </c>
       <c r="N97">
-        <v>141.394212</v>
+        <v>140.4583616</v>
       </c>
       <c r="O97">
-        <v>41.71129254</v>
+        <v>41.435216672</v>
       </c>
       <c r="P97">
-        <v>99.68291946000001</v>
+        <v>99.02314492799999</v>
       </c>
       <c r="Q97">
-        <v>135.78291946</v>
+        <v>135.123144928</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5842131211540073</v>
+        <v>0.7160579458895321</v>
       </c>
       <c r="T97">
-        <v>8.329079748360789</v>
+        <v>10.36867725534042</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.590382529425418</v>
+        <v>2.563399378077237</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07730423783558125</v>
+        <v>0.07724279461346216</v>
       </c>
       <c r="C98">
-        <v>90.8784920945152</v>
+        <v>79.17228882472887</v>
       </c>
       <c r="D98">
-        <v>1303.814492094515</v>
+        <v>1305.124288824729</v>
       </c>
       <c r="E98">
-        <v>677.9359999999998</v>
+        <v>690.9519999999999</v>
       </c>
       <c r="F98">
-        <v>1249.536</v>
+        <v>1262.552</v>
       </c>
       <c r="G98">
         <v>36.6</v>
@@ -9323,28 +9323,28 @@
         <v>230.3</v>
       </c>
       <c r="M98">
-        <v>89.84163839999999</v>
+        <v>90.7774888</v>
       </c>
       <c r="N98">
-        <v>140.4583616</v>
+        <v>139.5225112</v>
       </c>
       <c r="O98">
-        <v>41.435216672</v>
+        <v>41.159140804</v>
       </c>
       <c r="P98">
-        <v>99.02314492800002</v>
+        <v>98.36337039599999</v>
       </c>
       <c r="Q98">
-        <v>135.123144928</v>
+        <v>134.463370396</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7160579458895304</v>
+        <v>0.9357993204487375</v>
       </c>
       <c r="T98">
-        <v>10.3686772553404</v>
+        <v>13.76800643363977</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.563399378077237</v>
+        <v>2.5369725803651</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07724279461346216</v>
+        <v>0.07718135139134308</v>
       </c>
       <c r="C99">
-        <v>79.17228882472887</v>
+        <v>67.46871981412073</v>
       </c>
       <c r="D99">
-        <v>1305.124288824729</v>
+        <v>1306.436719814121</v>
       </c>
       <c r="E99">
-        <v>690.9519999999999</v>
+        <v>703.968</v>
       </c>
       <c r="F99">
-        <v>1262.552</v>
+        <v>1275.568</v>
       </c>
       <c r="G99">
         <v>36.6</v>
@@ -9405,28 +9405,28 @@
         <v>230.3</v>
       </c>
       <c r="M99">
-        <v>90.7774888</v>
+        <v>91.71333920000001</v>
       </c>
       <c r="N99">
-        <v>139.5225112</v>
+        <v>138.5866608</v>
       </c>
       <c r="O99">
-        <v>41.159140804</v>
+        <v>40.883064936</v>
       </c>
       <c r="P99">
-        <v>98.36337039599999</v>
+        <v>97.70359586400001</v>
       </c>
       <c r="Q99">
-        <v>134.463370396</v>
+        <v>133.803595864</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9357993204487375</v>
+        <v>1.375282069567152</v>
       </c>
       <c r="T99">
-        <v>13.76800643363977</v>
+        <v>20.56666479023853</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.5369725803651</v>
+        <v>2.511085105055252</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07718135139134308</v>
+        <v>0.07984191316922397</v>
       </c>
       <c r="C100">
-        <v>67.46871981412073</v>
+        <v>-0.06049123206071272</v>
       </c>
       <c r="D100">
-        <v>1306.436719814121</v>
+        <v>1251.923508767939</v>
       </c>
       <c r="E100">
-        <v>703.968</v>
+        <v>716.9839999999998</v>
       </c>
       <c r="F100">
-        <v>1275.568</v>
+        <v>1288.584</v>
       </c>
       <c r="G100">
         <v>36.6</v>
@@ -9487,129 +9487,47 @@
         <v>230.3</v>
       </c>
       <c r="M100">
-        <v>91.71333920000001</v>
+        <v>97.6746672</v>
       </c>
       <c r="N100">
-        <v>138.5866608</v>
+        <v>132.6253328</v>
       </c>
       <c r="O100">
-        <v>40.883064936</v>
+        <v>39.124473176</v>
       </c>
       <c r="P100">
-        <v>97.70359586400001</v>
+        <v>93.50085962400001</v>
       </c>
       <c r="Q100">
-        <v>133.803595864</v>
+        <v>129.600859624</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.375282069567152</v>
+        <v>2.693730316922394</v>
       </c>
       <c r="T100">
-        <v>20.56666479023853</v>
+        <v>40.96263986003478</v>
       </c>
       <c r="U100">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V100">
         <v>0.295</v>
       </c>
       <c r="W100">
-        <v>0.05068950000000001</v>
+        <v>0.05343900000000001</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y100">
-        <v>2.511085105055252</v>
+        <v>2.35782733232594</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07984191316922397</v>
-      </c>
-      <c r="C101">
-        <v>-0.06049123206071272</v>
-      </c>
-      <c r="D101">
-        <v>1251.923508767939</v>
-      </c>
-      <c r="E101">
-        <v>716.9839999999998</v>
-      </c>
-      <c r="F101">
-        <v>1288.584</v>
-      </c>
-      <c r="G101">
-        <v>36.6</v>
-      </c>
-      <c r="H101">
-        <v>730</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>266.4</v>
-      </c>
-      <c r="K101">
-        <v>36.09999999999997</v>
-      </c>
-      <c r="L101">
-        <v>230.3</v>
-      </c>
-      <c r="M101">
-        <v>97.6746672</v>
-      </c>
-      <c r="N101">
-        <v>132.6253328</v>
-      </c>
-      <c r="O101">
-        <v>39.124473176</v>
-      </c>
-      <c r="P101">
-        <v>93.50085962400001</v>
-      </c>
-      <c r="Q101">
-        <v>129.600859624</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.693730316922394</v>
-      </c>
-      <c r="T101">
-        <v>40.96263986003478</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.295</v>
-      </c>
-      <c r="W101">
-        <v>0.05343900000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.35782733232594</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
